--- a/turni.xlsx
+++ b/turni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pronto.soccorso\Desktop\AGGIORNA APP TURNI\AUTISTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C27CC7-3FB4-46B1-B413-BF96CE49E112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA2450A-786D-4E17-9F56-7DD6CF50E828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EED674EF-86D6-4082-A0C5-CB69D204F6EE}"/>
   </bookViews>
@@ -5337,7 +5337,7 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AT271" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="272">
@@ -5597,7 +5597,7 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR290" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS290" t="str">
             <v>GHIOTTI</v>
@@ -5628,32 +5628,32 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS292" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT292" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="293">
           <cell r="AQ293" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR293" t="str">
-            <v>MICHELOT.</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS293" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT293" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="294">
           <cell r="AQ294" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR294" t="str">
-            <v>BARBIERI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS294" t="str">
             <v>SARTI</v>
@@ -5684,18 +5684,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS296" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT296" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="297">
           <cell r="AQ297" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR297" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS297" t="str">
             <v>GHIOTTI</v>
@@ -5754,18 +5754,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS301" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AT301" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="302">
           <cell r="AQ302" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR302" t="str">
-            <v>FABBRI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS302" t="str">
             <v>BERARDI</v>
@@ -5824,18 +5824,18 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS306" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT306" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="307">
           <cell r="AQ307" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR307" t="str">
-            <v>GHIOTTI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS307" t="str">
             <v>PAZZAGLIA</v>
@@ -5852,32 +5852,32 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS308" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AT308" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
         </row>
         <row r="309">
           <cell r="AQ309" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AR309" t="str">
-            <v>BIANCHI</v>
+            <v>BERARDI</v>
           </cell>
           <cell r="AS309" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT309" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="310">
           <cell r="AQ310" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR310" t="str">
-            <v>SARTI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS310" t="str">
             <v>BARBIERI</v>
@@ -5891,21 +5891,21 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AR311" t="str">
+            <v>GHIOTTI</v>
+          </cell>
+          <cell r="AS311" t="str">
             <v>BARBIERI</v>
           </cell>
-          <cell r="AS311" t="str">
-            <v>BERARDI</v>
-          </cell>
           <cell r="AT311" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
         </row>
         <row r="312">
           <cell r="AQ312" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AR312" t="str">
-            <v>BERARDI</v>
+            <v>GHIOTTI</v>
           </cell>
           <cell r="AS312" t="str">
             <v>PAZZAGLIA</v>
@@ -5922,18 +5922,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS313" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT313" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="314">
           <cell r="AQ314" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR314" t="str">
-            <v>VOLPINI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS314" t="str">
             <v>GHIOTTI</v>
@@ -5978,18 +5978,18 @@
             <v>FABBRI</v>
           </cell>
           <cell r="AS317" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT317" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="318">
           <cell r="AQ318" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR318" t="str">
-            <v>PAZZAGLIA</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS318" t="str">
             <v>BIANCHI</v>
@@ -6034,32 +6034,32 @@
             <v>BARBIERI</v>
           </cell>
           <cell r="AS321" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AT321" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
         </row>
         <row r="322">
           <cell r="AQ322" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AR322" t="str">
-            <v>FABBRI</v>
+            <v>SARTI</v>
           </cell>
           <cell r="AS322" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AT322" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
         </row>
         <row r="323">
           <cell r="AQ323" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AR323" t="str">
-            <v>VOLPINI</v>
+            <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS323" t="str">
             <v>BIANCHI</v>
@@ -6118,18 +6118,18 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AS327" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT327" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="328">
           <cell r="AQ328" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR328" t="str">
-            <v>MICHELOT.</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS328" t="str">
             <v>VOLPINI</v>
@@ -6177,12 +6177,12 @@
             <v>BERARDI</v>
           </cell>
           <cell r="AT331" t="str">
-            <v>BERARDI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="332">
           <cell r="AQ332" t="str">
-            <v>BERARDI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR332" t="str">
             <v>BERARDI</v>
@@ -6202,32 +6202,32 @@
             <v>MICHELOT.</v>
           </cell>
           <cell r="AS333" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AT333" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
         </row>
         <row r="334">
           <cell r="AQ334" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AR334" t="str">
-            <v>FABBRI</v>
+            <v>VOLPINI</v>
           </cell>
           <cell r="AS334" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AT334" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
         </row>
         <row r="335">
           <cell r="AQ335" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AR335" t="str">
-            <v>GHIOTTI</v>
+            <v>BIANCHI</v>
           </cell>
           <cell r="AS335" t="str">
             <v>SARTI</v>
@@ -6244,18 +6244,18 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS336" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT336" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="337">
           <cell r="AQ337" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR337" t="str">
-            <v>BERARDI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS337" t="str">
             <v>PAZZAGLIA</v>
@@ -6272,18 +6272,18 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS338" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT338" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
         <row r="339">
           <cell r="AQ339" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AR339" t="str">
-            <v>MICHELOT.</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS339" t="str">
             <v>GHIOTTI</v>
@@ -6297,7 +6297,7 @@
             <v>GHIOTTI</v>
           </cell>
           <cell r="AR340" t="str">
-            <v>GHIOTTI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AS340" t="str">
             <v>SARTI</v>
@@ -6314,32 +6314,32 @@
             <v>SARTI</v>
           </cell>
           <cell r="AS341" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT341" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="342">
           <cell r="AQ342" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AR342" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AS342" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AT342" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
         </row>
         <row r="343">
           <cell r="AQ343" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AR343" t="str">
-            <v>BIANCHI</v>
+            <v>FABBRI</v>
           </cell>
           <cell r="AS343" t="str">
             <v>VOLPINI</v>
@@ -6629,6 +6629,12 @@
           </cell>
         </row>
         <row r="364">
+          <cell r="AQ364" t="str">
+            <v>VOLPINI</v>
+          </cell>
+          <cell r="AR364" t="str">
+            <v>VOLPINI</v>
+          </cell>
           <cell r="AS364" t="str">
             <v>GHIOTTI</v>
           </cell>
@@ -6686,13 +6692,19 @@
             <v>VOLPINI</v>
           </cell>
           <cell r="AS368" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
           <cell r="AT368" t="str">
-            <v>BERARDI</v>
+            <v>MICHELOT.</v>
           </cell>
         </row>
         <row r="369">
+          <cell r="AQ369" t="str">
+            <v>MICHELOT.</v>
+          </cell>
+          <cell r="AR369" t="str">
+            <v>MICHELOT.</v>
+          </cell>
           <cell r="AS369" t="str">
             <v>BARBIERI</v>
           </cell>
@@ -6736,10 +6748,10 @@
             <v>PAZZAGLIA</v>
           </cell>
           <cell r="AS372" t="str">
-            <v>BIANCHI</v>
+            <v>BARBIERI</v>
           </cell>
           <cell r="AT372" t="str">
-            <v>BIANCHI</v>
+            <v>BARBIERI</v>
           </cell>
         </row>
       </sheetData>
@@ -7569,7 +7581,7 @@
             <v>p</v>
           </cell>
           <cell r="JP3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="JQ3" t="str">
             <v>m</v>
@@ -7626,7 +7638,7 @@
             <v>S</v>
           </cell>
           <cell r="KI3" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="KJ3" t="str">
             <v>m</v>
@@ -7635,19 +7647,19 @@
             <v>p</v>
           </cell>
           <cell r="KL3" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="KM3" t="str">
             <v>r</v>
           </cell>
           <cell r="KN3" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KO3" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KP3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KO3" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KP3" t="str">
-            <v>r</v>
           </cell>
           <cell r="KQ3" t="str">
             <v>P</v>
@@ -7665,7 +7677,7 @@
             <v>R</v>
           </cell>
           <cell r="KV3" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="KW3" t="str">
             <v>M/R</v>
@@ -7683,22 +7695,22 @@
             <v>P</v>
           </cell>
           <cell r="LB3" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="LC3" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="LD3" t="str">
-            <v>S</v>
+            <v>p</v>
           </cell>
           <cell r="LE3" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="LF3" t="str">
             <v>P</v>
           </cell>
           <cell r="LG3" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LH3" t="str">
             <v>N</v>
@@ -7770,19 +7782,19 @@
             <v>R</v>
           </cell>
           <cell r="ME3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MF3" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="MG3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="MG3" t="str">
-            <v>m</v>
           </cell>
           <cell r="MH3" t="str">
             <v>p</v>
           </cell>
           <cell r="MI3" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="MJ3" t="str">
             <v>M/R</v>
@@ -7851,16 +7863,16 @@
             <v>p</v>
           </cell>
           <cell r="NF3" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NG3" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NG3" t="str">
-            <v>p</v>
           </cell>
           <cell r="NH3" t="str">
             <v>r</v>
           </cell>
           <cell r="NI3" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="NJ3" t="str">
             <v>m</v>
@@ -7908,16 +7920,16 @@
             <v>m</v>
           </cell>
           <cell r="NY3" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="NZ3" t="str">
             <v>p</v>
           </cell>
-          <cell r="NZ3" t="str">
-            <v>m</v>
-          </cell>
           <cell r="OA3" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="OB3" t="str">
             <v>p</v>
-          </cell>
-          <cell r="OB3" t="str">
-            <v>m</v>
           </cell>
           <cell r="OC3" t="str">
             <v>p</v>
@@ -8945,7 +8957,7 @@
             <v>0</v>
           </cell>
           <cell r="LZ4" t="str">
-            <v>f</v>
+            <v>p</v>
           </cell>
           <cell r="MA4" t="str">
             <v>f</v>
@@ -9631,7 +9643,7 @@
             <v>P</v>
           </cell>
           <cell r="FO6" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="FP6" t="str">
             <v>N</v>
@@ -9943,7 +9955,7 @@
             <v>r</v>
           </cell>
           <cell r="JO6" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="JP6" t="str">
             <v>M/R</v>
@@ -9967,13 +9979,13 @@
             <v>r</v>
           </cell>
           <cell r="JW6" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="JX6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="JY6" t="str">
             <v>p</v>
-          </cell>
-          <cell r="JX6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="JY6" t="str">
-            <v>m</v>
           </cell>
           <cell r="JZ6" t="str">
             <v>N</v>
@@ -9988,7 +10000,7 @@
             <v>r</v>
           </cell>
           <cell r="KD6" t="str">
-            <v>M/R</v>
+            <v>p</v>
           </cell>
           <cell r="KE6" t="str">
             <v>p</v>
@@ -9997,13 +10009,13 @@
             <v>m</v>
           </cell>
           <cell r="KG6" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="KH6" t="str">
             <v>r</v>
           </cell>
           <cell r="KI6" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="KJ6" t="str">
             <v>P</v>
@@ -10036,19 +10048,19 @@
             <v>R</v>
           </cell>
           <cell r="KT6" t="str">
-            <v>P</v>
+            <v>M</v>
           </cell>
           <cell r="KU6" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KV6" t="str">
-            <v>N</v>
+            <v>m/R</v>
           </cell>
           <cell r="KW6" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="KX6" t="str">
-            <v>R</v>
+            <v>p</v>
           </cell>
           <cell r="KY6" t="str">
             <v>P</v>
@@ -10111,34 +10123,34 @@
             <v>R</v>
           </cell>
           <cell r="LS6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LT6" t="str">
             <v>r</v>
           </cell>
-          <cell r="LT6" t="str">
-            <v>P</v>
-          </cell>
           <cell r="LU6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LV6" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LW6" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="LX6" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="LY6" t="str">
             <v>m</v>
           </cell>
-          <cell r="LV6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="LW6" t="str">
+          <cell r="LZ6" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="MA6" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="MB6" t="str">
             <v>r</v>
-          </cell>
-          <cell r="LX6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="LY6" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="LZ6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="MA6" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="MB6" t="str">
-            <v>p</v>
           </cell>
           <cell r="MC6" t="str">
             <v>m/R</v>
@@ -10147,19 +10159,19 @@
             <v>p</v>
           </cell>
           <cell r="ME6" t="str">
-            <v>m</v>
+            <v>M</v>
           </cell>
           <cell r="MF6" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="MG6" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="MH6" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="MI6" t="str">
             <v>p</v>
-          </cell>
-          <cell r="MH6" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="MI6" t="str">
-            <v>m</v>
           </cell>
           <cell r="MJ6" t="str">
             <v>m</v>
@@ -10213,10 +10225,10 @@
             <v>-</v>
           </cell>
           <cell r="NA6" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="NB6" t="str">
-            <v>m/R</v>
+            <v>M/R</v>
           </cell>
           <cell r="NC6" t="str">
             <v>p</v>
@@ -10225,7 +10237,7 @@
             <v>m</v>
           </cell>
           <cell r="NE6" t="str">
-            <v>r</v>
+            <v>M/R</v>
           </cell>
           <cell r="NF6" t="str">
             <v>N</v>
@@ -10255,7 +10267,7 @@
             <v>P</v>
           </cell>
           <cell r="NO6" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NP6" t="str">
             <v>N</v>
@@ -10267,31 +10279,31 @@
             <v>R</v>
           </cell>
           <cell r="NS6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NT6" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="NU6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="NV6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="NW6" t="str">
             <v>R</v>
           </cell>
           <cell r="NX6" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="NY6" t="str">
-            <v>M</v>
+            <v>-</v>
           </cell>
           <cell r="NZ6" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="OA6" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="OB6" t="str">
             <v>R</v>
@@ -10821,7 +10833,7 @@
             <v>0</v>
           </cell>
           <cell r="FO7">
-            <v>7</v>
+            <v>0</v>
           </cell>
           <cell r="FP7">
             <v>0</v>
@@ -11159,8 +11171,8 @@
           <cell r="JW7">
             <v>0</v>
           </cell>
-          <cell r="JX7">
-            <v>0</v>
+          <cell r="JX7" t="str">
+            <v>p</v>
           </cell>
           <cell r="JY7">
             <v>0</v>
@@ -11192,8 +11204,8 @@
           <cell r="KH7">
             <v>0</v>
           </cell>
-          <cell r="KI7">
-            <v>0</v>
+          <cell r="KI7" t="str">
+            <v>p</v>
           </cell>
           <cell r="KJ7">
             <v>0</v>
@@ -11300,17 +11312,17 @@
           <cell r="LR7">
             <v>0</v>
           </cell>
-          <cell r="LS7">
-            <v>0</v>
+          <cell r="LS7" t="str">
+            <v>R</v>
           </cell>
           <cell r="LT7">
             <v>0</v>
           </cell>
           <cell r="LU7">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LV7">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LW7">
             <v>0</v>
@@ -11456,32 +11468,32 @@
           <cell r="NR7">
             <v>0</v>
           </cell>
-          <cell r="NS7">
-            <v>0</v>
-          </cell>
-          <cell r="NT7">
-            <v>0</v>
-          </cell>
-          <cell r="NU7">
-            <v>0</v>
-          </cell>
-          <cell r="NV7">
-            <v>0</v>
-          </cell>
-          <cell r="NW7">
-            <v>0</v>
-          </cell>
-          <cell r="NX7">
-            <v>0</v>
-          </cell>
-          <cell r="NY7">
-            <v>0</v>
-          </cell>
-          <cell r="NZ7">
-            <v>0</v>
-          </cell>
-          <cell r="OA7">
-            <v>0</v>
+          <cell r="NS7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NT7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NU7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NV7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NW7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NX7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NY7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="NZ7" t="str">
+            <v>v</v>
+          </cell>
+          <cell r="OA7" t="str">
+            <v>v</v>
           </cell>
           <cell r="OB7">
             <v>0</v>
@@ -12368,7 +12380,7 @@
             <v>R</v>
           </cell>
           <cell r="KD9" t="str">
-            <v>P</v>
+            <v>r</v>
           </cell>
           <cell r="KE9" t="str">
             <v>M/R</v>
@@ -12380,7 +12392,7 @@
             <v>S</v>
           </cell>
           <cell r="KH9" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="KI9" t="str">
             <v>P</v>
@@ -12413,16 +12425,16 @@
             <v>R</v>
           </cell>
           <cell r="KS9" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="KT9" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="KU9" t="str">
-            <v>N</v>
+            <v>-</v>
           </cell>
           <cell r="KV9" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="KW9" t="str">
             <v>R</v>
@@ -12446,13 +12458,13 @@
             <v>-</v>
           </cell>
           <cell r="LD9" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="LE9" t="str">
             <v>p</v>
           </cell>
           <cell r="LF9" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="LG9" t="str">
             <v>p</v>
@@ -12470,7 +12482,7 @@
             <v>m</v>
           </cell>
           <cell r="LL9" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LM9" t="str">
             <v>p</v>
@@ -12485,10 +12497,10 @@
             <v>m</v>
           </cell>
           <cell r="LQ9" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="LR9" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="LS9" t="str">
             <v>P</v>
@@ -12614,13 +12626,13 @@
             <v>R</v>
           </cell>
           <cell r="NH9" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="NI9" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="NJ9" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NI9" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NJ9" t="str">
-            <v>r</v>
           </cell>
           <cell r="NK9" t="str">
             <v>p</v>
@@ -12629,13 +12641,13 @@
             <v>m</v>
           </cell>
           <cell r="NM9" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NN9" t="str">
             <v>r</v>
           </cell>
-          <cell r="NN9" t="str">
+          <cell r="NO9" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NO9" t="str">
-            <v>m/R</v>
           </cell>
           <cell r="NP9" t="str">
             <v>p</v>
@@ -12647,58 +12659,58 @@
             <v>p</v>
           </cell>
           <cell r="NS9" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NT9" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="NU9" t="str">
             <v>p</v>
           </cell>
-          <cell r="NT9" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NU9" t="str">
-            <v>m</v>
-          </cell>
           <cell r="NV9" t="str">
-            <v>p</v>
+            <v>N</v>
           </cell>
           <cell r="NW9" t="str">
-            <v>m</v>
+            <v>S</v>
           </cell>
           <cell r="NX9" t="str">
-            <v>p</v>
+            <v>R</v>
           </cell>
           <cell r="NY9" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="NZ9" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="OA9" t="str">
-            <v>m</v>
+            <v>N</v>
           </cell>
           <cell r="OB9" t="str">
-            <v>p</v>
+            <v>S</v>
           </cell>
           <cell r="OC9" t="str">
-            <v>m</v>
+            <v>R</v>
           </cell>
           <cell r="OD9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="OE9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
           <cell r="OF9" t="str">
-            <v>-</v>
+            <v>N</v>
           </cell>
           <cell r="OG9" t="str">
-            <v>-</v>
+            <v>S</v>
           </cell>
           <cell r="OH9" t="str">
-            <v>-</v>
+            <v>R</v>
           </cell>
           <cell r="OI9" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="OJ9" t="str">
-            <v>-</v>
+            <v>M</v>
           </cell>
         </row>
         <row r="10">
@@ -13602,17 +13614,17 @@
           <cell r="KR10">
             <v>0</v>
           </cell>
-          <cell r="KS10">
-            <v>0</v>
-          </cell>
-          <cell r="KT10">
-            <v>0</v>
-          </cell>
-          <cell r="KU10">
-            <v>0</v>
-          </cell>
-          <cell r="KV10">
-            <v>0</v>
+          <cell r="KS10" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KT10" t="str">
+            <v>f</v>
+          </cell>
+          <cell r="KU10" t="str">
+            <v>pn</v>
+          </cell>
+          <cell r="KV10" t="str">
+            <v>x</v>
           </cell>
           <cell r="KW10">
             <v>0</v>
@@ -13635,8 +13647,8 @@
           <cell r="LC10" t="str">
             <v>f</v>
           </cell>
-          <cell r="LD10" t="str">
-            <v>f</v>
+          <cell r="LD10">
+            <v>0</v>
           </cell>
           <cell r="LE10">
             <v>0</v>
@@ -14745,7 +14757,7 @@
             <v>S</v>
           </cell>
           <cell r="KC12" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="KD12" t="str">
             <v>r</v>
@@ -14772,13 +14784,13 @@
             <v>-</v>
           </cell>
           <cell r="KL12" t="str">
-            <v>p</v>
+            <v>P</v>
           </cell>
           <cell r="KM12" t="str">
             <v>m</v>
           </cell>
           <cell r="KN12" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KO12" t="str">
             <v>m</v>
@@ -14787,31 +14799,31 @@
             <v>-</v>
           </cell>
           <cell r="KQ12" t="str">
+            <v>r</v>
+          </cell>
+          <cell r="KR12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KR12" t="str">
-            <v>r</v>
-          </cell>
           <cell r="KS12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KT12" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="KU12" t="str">
             <v>p</v>
           </cell>
-          <cell r="KT12" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KU12" t="str">
+          <cell r="KV12" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="KW12" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="KX12" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="KY12" t="str">
             <v>m</v>
-          </cell>
-          <cell r="KV12" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KW12" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="KX12" t="str">
-            <v>m/R</v>
-          </cell>
-          <cell r="KY12" t="str">
-            <v>p</v>
           </cell>
           <cell r="KZ12" t="str">
             <v>p</v>
@@ -14820,22 +14832,22 @@
             <v>m</v>
           </cell>
           <cell r="LB12" t="str">
-            <v>p</v>
+            <v>M/R</v>
           </cell>
           <cell r="LC12" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="LD12" t="str">
-            <v>r</v>
+            <v>S</v>
           </cell>
           <cell r="LE12" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="LF12" t="str">
             <v>p</v>
           </cell>
           <cell r="LG12" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="LH12" t="str">
             <v>p</v>
@@ -14868,7 +14880,7 @@
             <v>P</v>
           </cell>
           <cell r="LR12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LS12" t="str">
             <v>N</v>
@@ -14880,10 +14892,10 @@
             <v>R</v>
           </cell>
           <cell r="LV12" t="str">
-            <v>r</v>
+            <v>P</v>
           </cell>
           <cell r="LW12" t="str">
-            <v>p</v>
+            <v>M</v>
           </cell>
           <cell r="LX12" t="str">
             <v>N</v>
@@ -14964,7 +14976,7 @@
             <v>p</v>
           </cell>
           <cell r="MX12" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="MY12" t="str">
             <v>P</v>
@@ -14988,16 +15000,16 @@
             <v>m</v>
           </cell>
           <cell r="NF12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NG12" t="str">
             <v>p</v>
           </cell>
-          <cell r="NG12" t="str">
+          <cell r="NH12" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="NI12" t="str">
             <v>r</v>
-          </cell>
-          <cell r="NH12" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="NI12" t="str">
-            <v>M/R</v>
           </cell>
           <cell r="NJ12" t="str">
             <v>N</v>
@@ -15042,7 +15054,7 @@
             <v>P</v>
           </cell>
           <cell r="NX12" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NY12" t="str">
             <v>N</v>
@@ -17071,7 +17083,7 @@
             <v>p</v>
           </cell>
           <cell r="JK15" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="JL15" t="str">
             <v>P</v>
@@ -17107,13 +17119,13 @@
             <v>P</v>
           </cell>
           <cell r="JW15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="JX15" t="str">
             <v>m</v>
           </cell>
-          <cell r="JX15" t="str">
+          <cell r="JY15" t="str">
             <v>r</v>
-          </cell>
-          <cell r="JY15" t="str">
-            <v>p</v>
           </cell>
           <cell r="JZ15" t="str">
             <v>p</v>
@@ -17128,7 +17140,7 @@
             <v>p</v>
           </cell>
           <cell r="KD15" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KE15" t="str">
             <v>r</v>
@@ -17152,7 +17164,7 @@
             <v>R</v>
           </cell>
           <cell r="KL15" t="str">
-            <v>P</v>
+            <v>m/R</v>
           </cell>
           <cell r="KM15" t="str">
             <v>p</v>
@@ -17161,31 +17173,31 @@
             <v>m</v>
           </cell>
           <cell r="KO15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KP15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KQ15" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="KR15" t="str">
             <v>r</v>
           </cell>
-          <cell r="KP15" t="str">
+          <cell r="KS15" t="str">
             <v>p</v>
           </cell>
-          <cell r="KQ15" t="str">
+          <cell r="KT15" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="KU15" t="str">
             <v>m/R</v>
           </cell>
-          <cell r="KR15" t="str">
+          <cell r="KV15" t="str">
             <v>p</v>
           </cell>
-          <cell r="KS15" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KT15" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KU15" t="str">
+          <cell r="KW15" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KV15" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="KW15" t="str">
-            <v>r</v>
           </cell>
           <cell r="KX15" t="str">
             <v>P</v>
@@ -17251,16 +17263,16 @@
             <v>r</v>
           </cell>
           <cell r="LS15" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="LT15" t="str">
-            <v>N</v>
+            <v>r</v>
           </cell>
           <cell r="LU15" t="str">
-            <v>S</v>
+            <v>p</v>
           </cell>
           <cell r="LV15" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="LW15" t="str">
             <v>P</v>
@@ -17332,7 +17344,7 @@
             <v>r</v>
           </cell>
           <cell r="MT15" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MU15" t="str">
             <v>m</v>
@@ -17356,7 +17368,7 @@
             <v>r</v>
           </cell>
           <cell r="NB15" t="str">
-            <v>P</v>
+            <v>p</v>
           </cell>
           <cell r="NC15" t="str">
             <v>M/R</v>
@@ -17404,7 +17416,7 @@
             <v>P</v>
           </cell>
           <cell r="NR15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NS15" t="str">
             <v>N</v>
@@ -17419,7 +17431,7 @@
             <v>P</v>
           </cell>
           <cell r="NW15" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NX15" t="str">
             <v>N</v>
@@ -18260,8 +18272,8 @@
           <cell r="JJ16">
             <v>0</v>
           </cell>
-          <cell r="JK16">
-            <v>0</v>
+          <cell r="JK16" t="str">
+            <v>k</v>
           </cell>
           <cell r="JL16">
             <v>0</v>
@@ -18440,8 +18452,8 @@
           <cell r="LR16">
             <v>0</v>
           </cell>
-          <cell r="LS16">
-            <v>0</v>
+          <cell r="LS16" t="str">
+            <v>p</v>
           </cell>
           <cell r="LT16">
             <v>0</v>
@@ -19463,7 +19475,7 @@
             <v>p</v>
           </cell>
           <cell r="JO18" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="JP18" t="str">
             <v>r</v>
@@ -19505,37 +19517,37 @@
             <v>P</v>
           </cell>
           <cell r="KC18" t="str">
-            <v>M/R</v>
+            <v>m</v>
           </cell>
           <cell r="KD18" t="str">
-            <v>N</v>
+            <v>m</v>
           </cell>
           <cell r="KE18" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="KF18" t="str">
-            <v>R</v>
+            <v>r</v>
           </cell>
           <cell r="KG18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KH18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KI18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KJ18" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="KK18" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="KL18" t="str">
-            <v>-</v>
+            <v>r</v>
           </cell>
           <cell r="KM18" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="KN18" t="str">
             <v>-</v>
@@ -19610,16 +19622,16 @@
             <v>-</v>
           </cell>
           <cell r="LL18" t="str">
-            <v>m/R</v>
+            <v>-</v>
           </cell>
           <cell r="LM18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="LN18" t="str">
-            <v>m</v>
+            <v>-</v>
           </cell>
           <cell r="LO18" t="str">
-            <v>r</v>
+            <v>R</v>
           </cell>
           <cell r="LP18" t="str">
             <v>p</v>
@@ -19634,25 +19646,25 @@
             <v>m</v>
           </cell>
           <cell r="LT18" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="LU18" t="str">
             <v>r</v>
           </cell>
           <cell r="LV18" t="str">
-            <v>r</v>
+            <v>N</v>
           </cell>
           <cell r="LW18" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="LX18" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="LY18" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="LZ18" t="str">
             <v>m/R</v>
-          </cell>
-          <cell r="LX18" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="LY18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="LZ18" t="str">
-            <v>r</v>
           </cell>
           <cell r="MA18" t="str">
             <v>p</v>
@@ -19661,7 +19673,7 @@
             <v>m</v>
           </cell>
           <cell r="MC18" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="MD18" t="str">
             <v>N</v>
@@ -19733,10 +19745,10 @@
             <v>R</v>
           </cell>
           <cell r="NA18" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="NB18" t="str">
             <v>P</v>
-          </cell>
-          <cell r="NB18" t="str">
-            <v>M</v>
           </cell>
           <cell r="NC18" t="str">
             <v>N</v>
@@ -19784,40 +19796,40 @@
             <v>p</v>
           </cell>
           <cell r="NR18" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="NS18" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="NT18" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="NU18" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="NV18" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="NW18" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="NX18" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="NY18" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="NZ18" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="OA18" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="OB18" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="OC18" t="str">
             <v>p</v>
-          </cell>
-          <cell r="NT18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NU18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NV18" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="NW18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NX18" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="NY18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="NZ18" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="OA18" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="OB18" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="OC18" t="str">
-            <v>m</v>
           </cell>
           <cell r="OD18" t="str">
             <v>-</v>
@@ -20706,41 +20718,41 @@
           <cell r="KF19">
             <v>0</v>
           </cell>
-          <cell r="KG19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KH19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KI19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KJ19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KK19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KL19" t="str">
-            <v>k</v>
-          </cell>
-          <cell r="KM19" t="str">
-            <v>k</v>
+          <cell r="KG19">
+            <v>0</v>
+          </cell>
+          <cell r="KH19">
+            <v>0</v>
+          </cell>
+          <cell r="KI19">
+            <v>0</v>
+          </cell>
+          <cell r="KJ19">
+            <v>0</v>
+          </cell>
+          <cell r="KK19">
+            <v>0</v>
+          </cell>
+          <cell r="KL19">
+            <v>0</v>
+          </cell>
+          <cell r="KM19">
+            <v>0</v>
           </cell>
           <cell r="KN19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KO19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KP19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KQ19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KR19" t="str">
-            <v>k</v>
+            <v>f</v>
           </cell>
           <cell r="KS19" t="str">
             <v>pn</v>
@@ -20799,17 +20811,17 @@
           <cell r="LK19" t="str">
             <v>f</v>
           </cell>
-          <cell r="LL19">
-            <v>0</v>
-          </cell>
-          <cell r="LM19">
-            <v>0</v>
-          </cell>
-          <cell r="LN19">
-            <v>0</v>
-          </cell>
-          <cell r="LO19">
-            <v>0</v>
+          <cell r="LL19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LM19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LN19" t="str">
+            <v>k</v>
+          </cell>
+          <cell r="LO19" t="str">
+            <v>k</v>
           </cell>
           <cell r="LP19">
             <v>0</v>
@@ -21885,19 +21897,19 @@
             <v>R</v>
           </cell>
           <cell r="KC21" t="str">
-            <v>P</v>
+            <v>M/R</v>
           </cell>
           <cell r="KD21" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="KE21" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="KF21" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="KG21" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KE21" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="KF21" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KG21" t="str">
-            <v>m/R</v>
           </cell>
           <cell r="KH21" t="str">
             <v>p</v>
@@ -21927,31 +21939,31 @@
             <v>R</v>
           </cell>
           <cell r="KQ21" t="str">
-            <v>r</v>
+            <v>p</v>
           </cell>
           <cell r="KR21" t="str">
             <v>P</v>
           </cell>
           <cell r="KS21" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="KT21" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="KU21" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="KV21" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="KW21" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="KX21" t="str">
             <v>m</v>
           </cell>
-          <cell r="KT21" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="KU21" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="KV21" t="str">
-            <v>m/R</v>
-          </cell>
-          <cell r="KW21" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="KX21" t="str">
+          <cell r="KY21" t="str">
             <v>p</v>
-          </cell>
-          <cell r="KY21" t="str">
-            <v>m</v>
           </cell>
           <cell r="KZ21" t="str">
             <v>m/R</v>
@@ -21963,7 +21975,7 @@
             <v>m</v>
           </cell>
           <cell r="LC21" t="str">
-            <v>r</v>
+            <v>m</v>
           </cell>
           <cell r="LD21" t="str">
             <v>P</v>
@@ -22014,25 +22026,25 @@
             <v>R</v>
           </cell>
           <cell r="LT21" t="str">
+            <v>P</v>
+          </cell>
+          <cell r="LU21" t="str">
+            <v>M</v>
+          </cell>
+          <cell r="LV21" t="str">
             <v>r</v>
           </cell>
-          <cell r="LU21" t="str">
-            <v>M/R</v>
-          </cell>
-          <cell r="LV21" t="str">
-            <v>N</v>
-          </cell>
           <cell r="LW21" t="str">
-            <v>S</v>
+            <v>-</v>
           </cell>
           <cell r="LX21" t="str">
-            <v>R</v>
+            <v>-</v>
           </cell>
           <cell r="LY21" t="str">
-            <v>P</v>
+            <v>-</v>
           </cell>
           <cell r="LZ21" t="str">
-            <v>M/R</v>
+            <v>r</v>
           </cell>
           <cell r="MA21" t="str">
             <v>N</v>
@@ -22044,19 +22056,19 @@
             <v>R</v>
           </cell>
           <cell r="MD21" t="str">
-            <v>P</v>
+            <v>m</v>
           </cell>
           <cell r="ME21" t="str">
-            <v>M/R</v>
+            <v>m/R</v>
           </cell>
           <cell r="MF21" t="str">
-            <v>N</v>
+            <v>p</v>
           </cell>
           <cell r="MG21" t="str">
-            <v>S</v>
+            <v>m</v>
           </cell>
           <cell r="MH21" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="MI21" t="str">
             <v>P</v>
@@ -22113,7 +22125,7 @@
             <v>P</v>
           </cell>
           <cell r="NA21" t="str">
-            <v>M/R</v>
+            <v>m</v>
           </cell>
           <cell r="NB21" t="str">
             <v>-</v>
@@ -22134,10 +22146,10 @@
             <v>-</v>
           </cell>
           <cell r="NH21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NI21" t="str">
             <v>m</v>
-          </cell>
-          <cell r="NI21" t="str">
-            <v>p</v>
           </cell>
           <cell r="NJ21" t="str">
             <v>r</v>
@@ -22149,13 +22161,13 @@
             <v>p</v>
           </cell>
           <cell r="NM21" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="NN21" t="str">
             <v>m</v>
           </cell>
-          <cell r="NN21" t="str">
+          <cell r="NO21" t="str">
             <v>r</v>
-          </cell>
-          <cell r="NO21" t="str">
-            <v>p</v>
           </cell>
           <cell r="NP21" t="str">
             <v>P</v>
@@ -22176,7 +22188,7 @@
             <v>P</v>
           </cell>
           <cell r="NV21" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="NW21" t="str">
             <v>N</v>
@@ -23213,13 +23225,13 @@
             <v>0</v>
           </cell>
           <cell r="LW22">
-            <v>0</v>
+            <v>6</v>
           </cell>
           <cell r="LX22">
-            <v>0</v>
-          </cell>
-          <cell r="LY22">
-            <v>0</v>
+            <v>6</v>
+          </cell>
+          <cell r="LY22" t="str">
+            <v>r</v>
           </cell>
           <cell r="LZ22">
             <v>0</v>
@@ -23318,7 +23330,7 @@
             <v>f</v>
           </cell>
           <cell r="NF22" t="str">
-            <v>V</v>
+            <v>nl</v>
           </cell>
           <cell r="NG22" t="str">
             <v>V</v>
@@ -24226,7 +24238,7 @@
             <v>r</v>
           </cell>
           <cell r="JP24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="JQ24" t="str">
             <v>N</v>
@@ -24265,10 +24277,10 @@
             <v>m</v>
           </cell>
           <cell r="KC24" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="KD24" t="str">
-            <v>r</v>
+            <v>M/R</v>
           </cell>
           <cell r="KE24" t="str">
             <v>N</v>
@@ -24313,7 +24325,7 @@
             <v>m</v>
           </cell>
           <cell r="KS24" t="str">
-            <v>M/R</v>
+            <v>P</v>
           </cell>
           <cell r="KT24" t="str">
             <v>N</v>
@@ -24325,10 +24337,10 @@
             <v>R</v>
           </cell>
           <cell r="KW24" t="str">
-            <v>-</v>
+            <v>P</v>
           </cell>
           <cell r="KX24" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KY24" t="str">
             <v>N</v>
@@ -24385,37 +24397,37 @@
             <v>r</v>
           </cell>
           <cell r="LQ24" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LR24" t="str">
+            <v>-</v>
+          </cell>
+          <cell r="LS24" t="str">
+            <v>M/R</v>
+          </cell>
+          <cell r="LT24" t="str">
+            <v>N</v>
+          </cell>
+          <cell r="LU24" t="str">
+            <v>S</v>
+          </cell>
+          <cell r="LV24" t="str">
+            <v>R</v>
+          </cell>
+          <cell r="LW24" t="str">
             <v>p</v>
           </cell>
-          <cell r="LR24" t="str">
+          <cell r="LX24" t="str">
+            <v>m</v>
+          </cell>
+          <cell r="LY24" t="str">
             <v>P</v>
-          </cell>
-          <cell r="LS24" t="str">
-            <v>m</v>
-          </cell>
-          <cell r="LT24" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="LU24" t="str">
-            <v>p</v>
-          </cell>
-          <cell r="LV24" t="str">
-            <v>P</v>
-          </cell>
-          <cell r="LW24" t="str">
-            <v>M</v>
-          </cell>
-          <cell r="LX24" t="str">
-            <v>r</v>
-          </cell>
-          <cell r="LY24" t="str">
-            <v>p</v>
           </cell>
           <cell r="LZ24" t="str">
             <v>P</v>
           </cell>
           <cell r="MA24" t="str">
-            <v>M/R</v>
+            <v>r</v>
           </cell>
           <cell r="MB24" t="str">
             <v>N</v>
@@ -24490,22 +24502,22 @@
             <v>-</v>
           </cell>
           <cell r="MZ24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NA24" t="str">
-            <v>-</v>
+            <v>p</v>
           </cell>
           <cell r="NB24" t="str">
-            <v>-</v>
+            <v>m</v>
           </cell>
           <cell r="NC24" t="str">
-            <v>R</v>
+            <v>m</v>
           </cell>
           <cell r="ND24" t="str">
             <v>P</v>
           </cell>
           <cell r="NE24" t="str">
-            <v>M/R</v>
+            <v>-</v>
           </cell>
           <cell r="NF24" t="str">
             <v>-</v>
@@ -24547,28 +24559,28 @@
             <v>R</v>
           </cell>
           <cell r="NS24" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="NT24" t="str">
             <v>p</v>
           </cell>
           <cell r="NU24" t="str">
+            <v>m/R</v>
+          </cell>
+          <cell r="NV24" t="str">
             <v>p</v>
           </cell>
-          <cell r="NV24" t="str">
+          <cell r="NW24" t="str">
             <v>m</v>
           </cell>
-          <cell r="NW24" t="str">
+          <cell r="NX24" t="str">
             <v>p</v>
           </cell>
-          <cell r="NX24" t="str">
+          <cell r="NY24" t="str">
             <v>m</v>
           </cell>
-          <cell r="NY24" t="str">
-            <v>p</v>
-          </cell>
           <cell r="NZ24" t="str">
-            <v>m</v>
+            <v>r</v>
           </cell>
           <cell r="OA24" t="str">
             <v>p</v>
@@ -24577,7 +24589,7 @@
             <v>m</v>
           </cell>
           <cell r="OC24" t="str">
-            <v>p</v>
+            <v>m</v>
           </cell>
           <cell r="OD24" t="str">
             <v>-</v>
@@ -25514,71 +25526,71 @@
           <cell r="KV25">
             <v>0</v>
           </cell>
-          <cell r="KW25" t="str">
+          <cell r="KW25">
+            <v>0</v>
+          </cell>
+          <cell r="KX25">
+            <v>0</v>
+          </cell>
+          <cell r="KY25">
+            <v>0</v>
+          </cell>
+          <cell r="KZ25">
+            <v>0</v>
+          </cell>
+          <cell r="LA25">
+            <v>0</v>
+          </cell>
+          <cell r="LB25">
+            <v>0</v>
+          </cell>
+          <cell r="LC25">
+            <v>0</v>
+          </cell>
+          <cell r="LD25">
+            <v>0</v>
+          </cell>
+          <cell r="LE25">
+            <v>0</v>
+          </cell>
+          <cell r="LF25">
+            <v>0</v>
+          </cell>
+          <cell r="LG25">
+            <v>0</v>
+          </cell>
+          <cell r="LH25">
+            <v>0</v>
+          </cell>
+          <cell r="LI25">
+            <v>0</v>
+          </cell>
+          <cell r="LJ25">
+            <v>0</v>
+          </cell>
+          <cell r="LK25">
+            <v>0</v>
+          </cell>
+          <cell r="LL25">
+            <v>0</v>
+          </cell>
+          <cell r="LM25">
+            <v>0</v>
+          </cell>
+          <cell r="LN25">
+            <v>0</v>
+          </cell>
+          <cell r="LO25">
+            <v>0</v>
+          </cell>
+          <cell r="LP25">
+            <v>0</v>
+          </cell>
+          <cell r="LQ25" t="str">
             <v>p</v>
           </cell>
-          <cell r="KX25">
-            <v>0</v>
-          </cell>
-          <cell r="KY25">
-            <v>0</v>
-          </cell>
-          <cell r="KZ25">
-            <v>0</v>
-          </cell>
-          <cell r="LA25">
-            <v>0</v>
-          </cell>
-          <cell r="LB25">
-            <v>0</v>
-          </cell>
-          <cell r="LC25">
-            <v>0</v>
-          </cell>
-          <cell r="LD25">
-            <v>0</v>
-          </cell>
-          <cell r="LE25">
-            <v>0</v>
-          </cell>
-          <cell r="LF25">
-            <v>0</v>
-          </cell>
-          <cell r="LG25">
-            <v>0</v>
-          </cell>
-          <cell r="LH25">
-            <v>0</v>
-          </cell>
-          <cell r="LI25">
-            <v>0</v>
-          </cell>
-          <cell r="LJ25">
-            <v>0</v>
-          </cell>
-          <cell r="LK25">
-            <v>0</v>
-          </cell>
-          <cell r="LL25">
-            <v>0</v>
-          </cell>
-          <cell r="LM25">
-            <v>0</v>
-          </cell>
-          <cell r="LN25">
-            <v>0</v>
-          </cell>
-          <cell r="LO25">
-            <v>0</v>
-          </cell>
-          <cell r="LP25">
-            <v>0</v>
-          </cell>
-          <cell r="LQ25">
-            <v>0</v>
-          </cell>
-          <cell r="LR25">
-            <v>0</v>
+          <cell r="LR25" t="str">
+            <v>p</v>
           </cell>
           <cell r="LS25">
             <v>0</v>
@@ -25677,16 +25689,16 @@
             <v>0</v>
           </cell>
           <cell r="MY25" t="str">
-            <v>nl</v>
-          </cell>
-          <cell r="MZ25" t="str">
-            <v>nl</v>
-          </cell>
-          <cell r="NA25" t="str">
-            <v>pn</v>
-          </cell>
-          <cell r="NB25" t="str">
-            <v>x</v>
+            <v>p</v>
+          </cell>
+          <cell r="MZ25">
+            <v>0</v>
+          </cell>
+          <cell r="NA25">
+            <v>0</v>
+          </cell>
+          <cell r="NB25">
+            <v>0</v>
           </cell>
           <cell r="NC25">
             <v>0</v>
@@ -25694,8 +25706,8 @@
           <cell r="ND25">
             <v>0</v>
           </cell>
-          <cell r="NE25">
-            <v>0</v>
+          <cell r="NE25" t="str">
+            <v>r</v>
           </cell>
           <cell r="NF25" t="str">
             <v>nl</v>
@@ -26657,7 +26669,7 @@
             <v>P</v>
           </cell>
           <cell r="KG27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KH27" t="str">
             <v>N</v>
@@ -26672,7 +26684,7 @@
             <v>P</v>
           </cell>
           <cell r="KL27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="KM27" t="str">
             <v>N</v>
@@ -26687,7 +26699,7 @@
             <v>P</v>
           </cell>
           <cell r="KQ27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="KR27" t="str">
             <v>N</v>
@@ -26732,7 +26744,7 @@
             <v>P</v>
           </cell>
           <cell r="LF27" t="str">
-            <v>M/R</v>
+            <v>M</v>
           </cell>
           <cell r="LG27" t="str">
             <v>N</v>
@@ -26750,7 +26762,7 @@
             <v>P</v>
           </cell>
           <cell r="LL27" t="str">
-            <v>M</v>
+            <v>M/R</v>
           </cell>
           <cell r="LM27" t="str">
             <v>N</v>
@@ -26762,22 +26774,22 @@
             <v>R</v>
           </cell>
           <cell r="LP27" t="str">
-            <v>r</v>
+            <v>-</v>
           </cell>
           <cell r="LQ27" t="str">
             <v>p</v>
           </cell>
           <cell r="LR27" t="str">
-            <v>m/R</v>
+            <v>m</v>
           </cell>
           <cell r="LS27" t="str">
             <v>p</v>
           </cell>
           <cell r="LT27" t="str">
-            <v>m</v>
+            <v>p</v>
           </cell>
           <cell r="LU27" t="str">
-            <v>r</v>
+            <v>m/R</v>
           </cell>
           <cell r="LV27" t="str">
             <v>p</v>
@@ -26795,16 +26807,16 @@
             <v>p</v>
           </cell>
           <cell r="MA27" t="str">
-            <v>m</v>
+            <v>m/R</v>
           </cell>
           <cell r="MB27" t="str">
+            <v>p</v>
+          </cell>
+          <cell r="MC27" t="str">
             <v>r</v>
           </cell>
-          <cell r="MC27" t="str">
-            <v>p</v>
-          </cell>
           <cell r="MD27" t="str">
-            <v>m</v>
+            <v>P</v>
           </cell>
           <cell r="ME27" t="str">
             <v>P</v>
@@ -27951,8 +27963,8 @@
           <cell r="LO28">
             <v>0</v>
           </cell>
-          <cell r="LP28">
-            <v>0</v>
+          <cell r="LP28" t="str">
+            <v>r</v>
           </cell>
           <cell r="LQ28">
             <v>0</v>
@@ -31228,7 +31240,7 @@
       </c>
       <c r="JM3" s="16" t="str">
         <f>[1]CARTELLINO!JP$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JN3" s="16" t="str">
         <f>[1]CARTELLINO!JQ$3</f>
@@ -31304,7 +31316,7 @@
       </c>
       <c r="KF3" s="16" t="str">
         <f>[1]CARTELLINO!KI$3</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="KG3" s="16" t="str">
         <f>[1]CARTELLINO!KJ$3</f>
@@ -31316,7 +31328,7 @@
       </c>
       <c r="KI3" s="16" t="str">
         <f>[1]CARTELLINO!KL$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KJ3" s="16" t="str">
         <f>[1]CARTELLINO!KM$3</f>
@@ -31324,15 +31336,15 @@
       </c>
       <c r="KK3" s="16" t="str">
         <f>[1]CARTELLINO!KN$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KL3" s="16" t="str">
         <f>[1]CARTELLINO!KO$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KM3" s="16" t="str">
         <f>[1]CARTELLINO!KP$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KN3" s="16" t="str">
         <f>[1]CARTELLINO!KQ$3</f>
@@ -31356,7 +31368,7 @@
       </c>
       <c r="KS3" s="16" t="str">
         <f>[1]CARTELLINO!KV$3</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="KT3" s="16" t="str">
         <f>[1]CARTELLINO!KW$3</f>
@@ -31380,19 +31392,19 @@
       </c>
       <c r="KY3" s="16" t="str">
         <f>[1]CARTELLINO!LB$3</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="KZ3" s="16" t="str">
         <f>[1]CARTELLINO!LC$3</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="LA3" s="16" t="str">
         <f>[1]CARTELLINO!LD$3</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="LB3" s="16" t="str">
         <f>[1]CARTELLINO!LE$3</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="LC3" s="16" t="str">
         <f>[1]CARTELLINO!LF$3</f>
@@ -31400,7 +31412,7 @@
       </c>
       <c r="LD3" s="16" t="str">
         <f>[1]CARTELLINO!LG$3</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LE3" s="16" t="str">
         <f>[1]CARTELLINO!LH$3</f>
@@ -31496,15 +31508,15 @@
       </c>
       <c r="MB3" s="16" t="str">
         <f>[1]CARTELLINO!ME$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MC3" s="16" t="str">
         <f>[1]CARTELLINO!MF$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MD3" s="16" t="str">
         <f>[1]CARTELLINO!MG$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="ME3" s="16" t="str">
         <f>[1]CARTELLINO!MH$3</f>
@@ -31512,7 +31524,7 @@
       </c>
       <c r="MF3" s="16" t="str">
         <f>[1]CARTELLINO!MI$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="MG3" s="16" t="str">
         <f>[1]CARTELLINO!MJ$3</f>
@@ -31604,11 +31616,11 @@
       </c>
       <c r="NC3" s="16" t="str">
         <f>[1]CARTELLINO!NF$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="ND3" s="16" t="str">
         <f>[1]CARTELLINO!NG$3</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NE3" s="16" t="str">
         <f>[1]CARTELLINO!NH$3</f>
@@ -31616,7 +31628,7 @@
       </c>
       <c r="NF3" s="16" t="str">
         <f>[1]CARTELLINO!NI$3</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NG3" s="16" t="str">
         <f>[1]CARTELLINO!NJ$3</f>
@@ -31680,19 +31692,19 @@
       </c>
       <c r="NV3" s="16" t="str">
         <f>[1]CARTELLINO!NY$3</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NW3" s="16" t="str">
         <f>[1]CARTELLINO!NZ$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NX3" s="16" t="str">
         <f>[1]CARTELLINO!OA$3</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="NY3" s="16" t="str">
         <f>[1]CARTELLINO!OB$3</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NZ3" s="16" t="str">
         <f>[1]CARTELLINO!OC$3</f>
@@ -33070,7 +33082,7 @@
       </c>
       <c r="LW4" s="43" t="str">
         <f>[1]CARTELLINO!LZ$4</f>
-        <v>f</v>
+        <v>p</v>
       </c>
       <c r="LX4" s="43" t="str">
         <f>[1]CARTELLINO!MA$4</f>
@@ -34403,7 +34415,7 @@
       </c>
       <c r="FL6" s="22" t="str">
         <f>[1]CARTELLINO!FO$6</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="FM6" s="22" t="str">
         <f>[1]CARTELLINO!FP$6</f>
@@ -34819,7 +34831,7 @@
       </c>
       <c r="JL6" s="22" t="str">
         <f>[1]CARTELLINO!JO$6</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="JM6" s="22" t="str">
         <f>[1]CARTELLINO!JP$6</f>
@@ -34851,15 +34863,15 @@
       </c>
       <c r="JT6" s="22" t="str">
         <f>[1]CARTELLINO!JW$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JU6" s="22" t="str">
         <f>[1]CARTELLINO!JX$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JV6" s="22" t="str">
         <f>[1]CARTELLINO!JY$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JW6" s="22" t="str">
         <f>[1]CARTELLINO!JZ$6</f>
@@ -34879,7 +34891,7 @@
       </c>
       <c r="KA6" s="22" t="str">
         <f>[1]CARTELLINO!KD$6</f>
-        <v>M/R</v>
+        <v>p</v>
       </c>
       <c r="KB6" s="22" t="str">
         <f>[1]CARTELLINO!KE$6</f>
@@ -34891,7 +34903,7 @@
       </c>
       <c r="KD6" s="22" t="str">
         <f>[1]CARTELLINO!KG$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KE6" s="22" t="str">
         <f>[1]CARTELLINO!KH$6</f>
@@ -34899,7 +34911,7 @@
       </c>
       <c r="KF6" s="22" t="str">
         <f>[1]CARTELLINO!KI$6</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="KG6" s="22" t="str">
         <f>[1]CARTELLINO!KJ$6</f>
@@ -34943,23 +34955,23 @@
       </c>
       <c r="KQ6" s="22" t="str">
         <f>[1]CARTELLINO!KT$6</f>
-        <v>P</v>
+        <v>M</v>
       </c>
       <c r="KR6" s="22" t="str">
         <f>[1]CARTELLINO!KU$6</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KS6" s="22" t="str">
         <f>[1]CARTELLINO!KV$6</f>
-        <v>N</v>
+        <v>m/R</v>
       </c>
       <c r="KT6" s="22" t="str">
         <f>[1]CARTELLINO!KW$6</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="KU6" s="22" t="str">
         <f>[1]CARTELLINO!KX$6</f>
-        <v>R</v>
+        <v>p</v>
       </c>
       <c r="KV6" s="22" t="str">
         <f>[1]CARTELLINO!KY$6</f>
@@ -35043,43 +35055,43 @@
       </c>
       <c r="LP6" s="22" t="str">
         <f>[1]CARTELLINO!LS$6</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="LQ6" s="22" t="str">
         <f>[1]CARTELLINO!LT$6</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="LR6" s="22" t="str">
         <f>[1]CARTELLINO!LU$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LS6" s="22" t="str">
         <f>[1]CARTELLINO!LV$6</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LT6" s="22" t="str">
         <f>[1]CARTELLINO!LW$6</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="LU6" s="22" t="str">
         <f>[1]CARTELLINO!LX$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LV6" s="22" t="str">
         <f>[1]CARTELLINO!LY$6</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LW6" s="22" t="str">
         <f>[1]CARTELLINO!LZ$6</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="LX6" s="22" t="str">
         <f>[1]CARTELLINO!MA$6</f>
-        <v>r</v>
+        <v>M</v>
       </c>
       <c r="LY6" s="22" t="str">
         <f>[1]CARTELLINO!MB$6</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="LZ6" s="22" t="str">
         <f>[1]CARTELLINO!MC$6</f>
@@ -35091,23 +35103,23 @@
       </c>
       <c r="MB6" s="22" t="str">
         <f>[1]CARTELLINO!ME$6</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="MC6" s="22" t="str">
         <f>[1]CARTELLINO!MF$6</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="MD6" s="22" t="str">
         <f>[1]CARTELLINO!MG$6</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="ME6" s="22" t="str">
         <f>[1]CARTELLINO!MH$6</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="MF6" s="22" t="str">
         <f>[1]CARTELLINO!MI$6</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="MG6" s="22" t="str">
         <f>[1]CARTELLINO!MJ$6</f>
@@ -35179,11 +35191,11 @@
       </c>
       <c r="MX6" s="22" t="str">
         <f>[1]CARTELLINO!NA$6</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="MY6" s="22" t="str">
         <f>[1]CARTELLINO!NB$6</f>
-        <v>m/R</v>
+        <v>M/R</v>
       </c>
       <c r="MZ6" s="22" t="str">
         <f>[1]CARTELLINO!NC$6</f>
@@ -35195,7 +35207,7 @@
       </c>
       <c r="NB6" s="22" t="str">
         <f>[1]CARTELLINO!NE$6</f>
-        <v>r</v>
+        <v>M/R</v>
       </c>
       <c r="NC6" s="22" t="str">
         <f>[1]CARTELLINO!NF$6</f>
@@ -35235,7 +35247,7 @@
       </c>
       <c r="NL6" s="22" t="str">
         <f>[1]CARTELLINO!NO$6</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NM6" s="22" t="str">
         <f>[1]CARTELLINO!NP$6</f>
@@ -35251,19 +35263,19 @@
       </c>
       <c r="NP6" s="22" t="str">
         <f>[1]CARTELLINO!NS$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="NQ6" s="22" t="str">
         <f>[1]CARTELLINO!NT$6</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="NR6" s="22" t="str">
         <f>[1]CARTELLINO!NU$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NS6" s="22" t="str">
         <f>[1]CARTELLINO!NV$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NT6" s="22" t="str">
         <f>[1]CARTELLINO!NW$6</f>
@@ -35271,19 +35283,19 @@
       </c>
       <c r="NU6" s="22" t="str">
         <f>[1]CARTELLINO!NX$6</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="NV6" s="22" t="str">
         <f>[1]CARTELLINO!NY$6</f>
-        <v>M</v>
+        <v>-</v>
       </c>
       <c r="NW6" s="22" t="str">
         <f>[1]CARTELLINO!NZ$6</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="NX6" s="22" t="str">
         <f>[1]CARTELLINO!OA$6</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="NY6" s="22" t="str">
         <f>[1]CARTELLINO!OB$6</f>
@@ -35997,7 +36009,7 @@
       </c>
       <c r="FL7" s="46">
         <f>[1]CARTELLINO!FO$7</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="FM7" s="46">
         <f>[1]CARTELLINO!FP$7</f>
@@ -36447,9 +36459,9 @@
         <f>[1]CARTELLINO!JW$7</f>
         <v>0</v>
       </c>
-      <c r="JU7" s="46">
+      <c r="JU7" s="46" t="str">
         <f>[1]CARTELLINO!JX$7</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="JV7" s="46">
         <f>[1]CARTELLINO!JY$7</f>
@@ -36491,9 +36503,9 @@
         <f>[1]CARTELLINO!KH$7</f>
         <v>0</v>
       </c>
-      <c r="KF7" s="46">
+      <c r="KF7" s="46" t="str">
         <f>[1]CARTELLINO!KI$7</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="KG7" s="46">
         <f>[1]CARTELLINO!KJ$7</f>
@@ -36635,9 +36647,9 @@
         <f>[1]CARTELLINO!LR$7</f>
         <v>0</v>
       </c>
-      <c r="LP7" s="46">
+      <c r="LP7" s="46" t="str">
         <f>[1]CARTELLINO!LS$7</f>
-        <v>0</v>
+        <v>R</v>
       </c>
       <c r="LQ7" s="46">
         <f>[1]CARTELLINO!LT$7</f>
@@ -36645,11 +36657,11 @@
       </c>
       <c r="LR7" s="46">
         <f>[1]CARTELLINO!LU$7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LS7" s="46">
         <f>[1]CARTELLINO!LV$7</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LT7" s="46">
         <f>[1]CARTELLINO!LW$7</f>
@@ -36843,41 +36855,41 @@
         <f>[1]CARTELLINO!NR$7</f>
         <v>0</v>
       </c>
-      <c r="NP7" s="46">
+      <c r="NP7" s="46" t="str">
         <f>[1]CARTELLINO!NS$7</f>
-        <v>0</v>
-      </c>
-      <c r="NQ7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NQ7" s="46" t="str">
         <f>[1]CARTELLINO!NT$7</f>
-        <v>0</v>
-      </c>
-      <c r="NR7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NR7" s="46" t="str">
         <f>[1]CARTELLINO!NU$7</f>
-        <v>0</v>
-      </c>
-      <c r="NS7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NS7" s="46" t="str">
         <f>[1]CARTELLINO!NV$7</f>
-        <v>0</v>
-      </c>
-      <c r="NT7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NT7" s="46" t="str">
         <f>[1]CARTELLINO!NW$7</f>
-        <v>0</v>
-      </c>
-      <c r="NU7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NU7" s="46" t="str">
         <f>[1]CARTELLINO!NX$7</f>
-        <v>0</v>
-      </c>
-      <c r="NV7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NV7" s="46" t="str">
         <f>[1]CARTELLINO!NY$7</f>
-        <v>0</v>
-      </c>
-      <c r="NW7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NW7" s="46" t="str">
         <f>[1]CARTELLINO!NZ$7</f>
-        <v>0</v>
-      </c>
-      <c r="NX7" s="46">
+        <v>v</v>
+      </c>
+      <c r="NX7" s="46" t="str">
         <f>[1]CARTELLINO!OA$7</f>
-        <v>0</v>
+        <v>v</v>
       </c>
       <c r="NY7" s="46">
         <f>[1]CARTELLINO!OB$7</f>
@@ -38475,7 +38487,7 @@
       </c>
       <c r="KA9" s="24" t="str">
         <f>[1]CARTELLINO!KD$9</f>
-        <v>P</v>
+        <v>r</v>
       </c>
       <c r="KB9" s="24" t="str">
         <f>[1]CARTELLINO!KE$9</f>
@@ -38491,7 +38503,7 @@
       </c>
       <c r="KE9" s="24" t="str">
         <f>[1]CARTELLINO!KH$9</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="KF9" s="24" t="str">
         <f>[1]CARTELLINO!KI$9</f>
@@ -38535,19 +38547,19 @@
       </c>
       <c r="KP9" s="24" t="str">
         <f>[1]CARTELLINO!KS$9</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="KQ9" s="24" t="str">
         <f>[1]CARTELLINO!KT$9</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="KR9" s="24" t="str">
         <f>[1]CARTELLINO!KU$9</f>
-        <v>N</v>
+        <v>-</v>
       </c>
       <c r="KS9" s="24" t="str">
         <f>[1]CARTELLINO!KV$9</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="KT9" s="24" t="str">
         <f>[1]CARTELLINO!KW$9</f>
@@ -38579,7 +38591,7 @@
       </c>
       <c r="LA9" s="24" t="str">
         <f>[1]CARTELLINO!LD$9</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="LB9" s="24" t="str">
         <f>[1]CARTELLINO!LE$9</f>
@@ -38587,7 +38599,7 @@
       </c>
       <c r="LC9" s="24" t="str">
         <f>[1]CARTELLINO!LF$9</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LD9" s="24" t="str">
         <f>[1]CARTELLINO!LG$9</f>
@@ -38611,7 +38623,7 @@
       </c>
       <c r="LI9" s="24" t="str">
         <f>[1]CARTELLINO!LL$9</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LJ9" s="24" t="str">
         <f>[1]CARTELLINO!LM$9</f>
@@ -38631,11 +38643,11 @@
       </c>
       <c r="LN9" s="24" t="str">
         <f>[1]CARTELLINO!LQ$9</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="LO9" s="24" t="str">
         <f>[1]CARTELLINO!LR$9</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LP9" s="24" t="str">
         <f>[1]CARTELLINO!LS$9</f>
@@ -38803,15 +38815,15 @@
       </c>
       <c r="NE9" s="24" t="str">
         <f>[1]CARTELLINO!NH$9</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NF9" s="24" t="str">
         <f>[1]CARTELLINO!NI$9</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="NG9" s="24" t="str">
         <f>[1]CARTELLINO!NJ$9</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NH9" s="24" t="str">
         <f>[1]CARTELLINO!NK$9</f>
@@ -38823,15 +38835,15 @@
       </c>
       <c r="NJ9" s="24" t="str">
         <f>[1]CARTELLINO!NM$9</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="NK9" s="24" t="str">
         <f>[1]CARTELLINO!NN$9</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NL9" s="24" t="str">
         <f>[1]CARTELLINO!NO$9</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="NM9" s="24" t="str">
         <f>[1]CARTELLINO!NP$9</f>
@@ -38847,75 +38859,75 @@
       </c>
       <c r="NP9" s="24" t="str">
         <f>[1]CARTELLINO!NS$9</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NQ9" s="24" t="str">
         <f>[1]CARTELLINO!NT$9</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="NR9" s="24" t="str">
         <f>[1]CARTELLINO!NU$9</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NS9" s="24" t="str">
         <f>[1]CARTELLINO!NV$9</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="NT9" s="24" t="str">
         <f>[1]CARTELLINO!NW$9</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="NU9" s="24" t="str">
         <f>[1]CARTELLINO!NX$9</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="NV9" s="24" t="str">
         <f>[1]CARTELLINO!NY$9</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="NW9" s="24" t="str">
         <f>[1]CARTELLINO!NZ$9</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="NX9" s="24" t="str">
         <f>[1]CARTELLINO!OA$9</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="NY9" s="24" t="str">
         <f>[1]CARTELLINO!OB$9</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="NZ9" s="24" t="str">
         <f>[1]CARTELLINO!OC$9</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="OA9" s="24" t="str">
         <f>[1]CARTELLINO!OD$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="OB9" s="24" t="str">
         <f>[1]CARTELLINO!OE$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="OC9" s="24" t="str">
         <f>[1]CARTELLINO!OF$9</f>
-        <v>-</v>
+        <v>N</v>
       </c>
       <c r="OD9" s="24" t="str">
         <f>[1]CARTELLINO!OG$9</f>
-        <v>-</v>
+        <v>S</v>
       </c>
       <c r="OE9" s="24" t="str">
         <f>[1]CARTELLINO!OH$9</f>
-        <v>-</v>
+        <v>R</v>
       </c>
       <c r="OF9" s="24" t="str">
         <f>[1]CARTELLINO!OI$9</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="OG9" s="24" t="str">
         <f>[1]CARTELLINO!OJ$9</f>
-        <v>-</v>
+        <v>M</v>
       </c>
       <c r="OH9" s="17"/>
       <c r="OI9" s="17"/>
@@ -40127,21 +40139,21 @@
         <f>[1]CARTELLINO!KR$10</f>
         <v>0</v>
       </c>
-      <c r="KP10" s="46">
+      <c r="KP10" s="46" t="str">
         <f>[1]CARTELLINO!KS$10</f>
-        <v>0</v>
-      </c>
-      <c r="KQ10" s="46">
+        <v>f</v>
+      </c>
+      <c r="KQ10" s="46" t="str">
         <f>[1]CARTELLINO!KT$10</f>
-        <v>0</v>
-      </c>
-      <c r="KR10" s="46">
+        <v>f</v>
+      </c>
+      <c r="KR10" s="46" t="str">
         <f>[1]CARTELLINO!KU$10</f>
-        <v>0</v>
-      </c>
-      <c r="KS10" s="46">
+        <v>pn</v>
+      </c>
+      <c r="KS10" s="46" t="str">
         <f>[1]CARTELLINO!KV$10</f>
-        <v>0</v>
+        <v>x</v>
       </c>
       <c r="KT10" s="46">
         <f>[1]CARTELLINO!KW$10</f>
@@ -40171,9 +40183,9 @@
         <f>[1]CARTELLINO!LC$10</f>
         <v>f</v>
       </c>
-      <c r="LA10" s="46" t="str">
+      <c r="LA10" s="46">
         <f>[1]CARTELLINO!LD$10</f>
-        <v>f</v>
+        <v>0</v>
       </c>
       <c r="LB10" s="46">
         <f>[1]CARTELLINO!LE$10</f>
@@ -42067,7 +42079,7 @@
       </c>
       <c r="JZ12" s="25" t="str">
         <f>[1]CARTELLINO!KC$12</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="KA12" s="25" t="str">
         <f>[1]CARTELLINO!KD$12</f>
@@ -42103,7 +42115,7 @@
       </c>
       <c r="KI12" s="25" t="str">
         <f>[1]CARTELLINO!KL$12</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="KJ12" s="25" t="str">
         <f>[1]CARTELLINO!KM$12</f>
@@ -42111,7 +42123,7 @@
       </c>
       <c r="KK12" s="25" t="str">
         <f>[1]CARTELLINO!KN$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KL12" s="25" t="str">
         <f>[1]CARTELLINO!KO$12</f>
@@ -42123,39 +42135,39 @@
       </c>
       <c r="KN12" s="25" t="str">
         <f>[1]CARTELLINO!KQ$12</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KO12" s="25" t="str">
         <f>[1]CARTELLINO!KR$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KP12" s="25" t="str">
         <f>[1]CARTELLINO!KS$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KQ12" s="25" t="str">
         <f>[1]CARTELLINO!KT$12</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KR12" s="25" t="str">
         <f>[1]CARTELLINO!KU$12</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KS12" s="25" t="str">
         <f>[1]CARTELLINO!KV$12</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="KT12" s="25" t="str">
         <f>[1]CARTELLINO!KW$12</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="KU12" s="25" t="str">
         <f>[1]CARTELLINO!KX$12</f>
-        <v>m/R</v>
+        <v>R</v>
       </c>
       <c r="KV12" s="25" t="str">
         <f>[1]CARTELLINO!KY$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KW12" s="25" t="str">
         <f>[1]CARTELLINO!KZ$12</f>
@@ -42167,19 +42179,19 @@
       </c>
       <c r="KY12" s="25" t="str">
         <f>[1]CARTELLINO!LB$12</f>
-        <v>p</v>
+        <v>M/R</v>
       </c>
       <c r="KZ12" s="25" t="str">
         <f>[1]CARTELLINO!LC$12</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="LA12" s="25" t="str">
         <f>[1]CARTELLINO!LD$12</f>
-        <v>r</v>
+        <v>S</v>
       </c>
       <c r="LB12" s="25" t="str">
         <f>[1]CARTELLINO!LE$12</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="LC12" s="25" t="str">
         <f>[1]CARTELLINO!LF$12</f>
@@ -42187,7 +42199,7 @@
       </c>
       <c r="LD12" s="25" t="str">
         <f>[1]CARTELLINO!LG$12</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="LE12" s="25" t="str">
         <f>[1]CARTELLINO!LH$12</f>
@@ -42231,7 +42243,7 @@
       </c>
       <c r="LO12" s="25" t="str">
         <f>[1]CARTELLINO!LR$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LP12" s="25" t="str">
         <f>[1]CARTELLINO!LS$12</f>
@@ -42247,11 +42259,11 @@
       </c>
       <c r="LS12" s="25" t="str">
         <f>[1]CARTELLINO!LV$12</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LT12" s="25" t="str">
         <f>[1]CARTELLINO!LW$12</f>
-        <v>p</v>
+        <v>M</v>
       </c>
       <c r="LU12" s="25" t="str">
         <f>[1]CARTELLINO!LX$12</f>
@@ -42359,7 +42371,7 @@
       </c>
       <c r="MU12" s="25" t="str">
         <f>[1]CARTELLINO!MX$12</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="MV12" s="25" t="str">
         <f>[1]CARTELLINO!MY$12</f>
@@ -42391,19 +42403,19 @@
       </c>
       <c r="NC12" s="25" t="str">
         <f>[1]CARTELLINO!NF$12</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="ND12" s="25" t="str">
         <f>[1]CARTELLINO!NG$12</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="NE12" s="25" t="str">
         <f>[1]CARTELLINO!NH$12</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="NF12" s="25" t="str">
         <f>[1]CARTELLINO!NI$12</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="NG12" s="25" t="str">
         <f>[1]CARTELLINO!NJ$12</f>
@@ -42463,7 +42475,7 @@
       </c>
       <c r="NU12" s="25" t="str">
         <f>[1]CARTELLINO!NX$12</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NV12" s="25" t="str">
         <f>[1]CARTELLINO!NY$12</f>
@@ -45591,7 +45603,7 @@
       </c>
       <c r="JH15" s="26" t="str">
         <f>[1]CARTELLINO!JK$15</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="JI15" s="26" t="str">
         <f>[1]CARTELLINO!JL$15</f>
@@ -45639,15 +45651,15 @@
       </c>
       <c r="JT15" s="26" t="str">
         <f>[1]CARTELLINO!JW$15</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="JU15" s="26" t="str">
         <f>[1]CARTELLINO!JX$15</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="JV15" s="26" t="str">
         <f>[1]CARTELLINO!JY$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="JW15" s="26" t="str">
         <f>[1]CARTELLINO!JZ$15</f>
@@ -45667,7 +45679,7 @@
       </c>
       <c r="KA15" s="26" t="str">
         <f>[1]CARTELLINO!KD$15</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KB15" s="26" t="str">
         <f>[1]CARTELLINO!KE$15</f>
@@ -45699,7 +45711,7 @@
       </c>
       <c r="KI15" s="26" t="str">
         <f>[1]CARTELLINO!KL$15</f>
-        <v>P</v>
+        <v>m/R</v>
       </c>
       <c r="KJ15" s="26" t="str">
         <f>[1]CARTELLINO!KM$15</f>
@@ -45711,39 +45723,39 @@
       </c>
       <c r="KL15" s="26" t="str">
         <f>[1]CARTELLINO!KO$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KM15" s="26" t="str">
         <f>[1]CARTELLINO!KP$15</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KN15" s="26" t="str">
         <f>[1]CARTELLINO!KQ$15</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="KO15" s="26" t="str">
         <f>[1]CARTELLINO!KR$15</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="KP15" s="26" t="str">
         <f>[1]CARTELLINO!KS$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KQ15" s="26" t="str">
         <f>[1]CARTELLINO!KT$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KR15" s="26" t="str">
         <f>[1]CARTELLINO!KU$15</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="KS15" s="26" t="str">
         <f>[1]CARTELLINO!KV$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="KT15" s="26" t="str">
         <f>[1]CARTELLINO!KW$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KU15" s="26" t="str">
         <f>[1]CARTELLINO!KX$15</f>
@@ -45831,19 +45843,19 @@
       </c>
       <c r="LP15" s="26" t="str">
         <f>[1]CARTELLINO!LS$15</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="LQ15" s="26" t="str">
         <f>[1]CARTELLINO!LT$15</f>
-        <v>N</v>
+        <v>r</v>
       </c>
       <c r="LR15" s="26" t="str">
         <f>[1]CARTELLINO!LU$15</f>
-        <v>S</v>
+        <v>p</v>
       </c>
       <c r="LS15" s="26" t="str">
         <f>[1]CARTELLINO!LV$15</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="LT15" s="26" t="str">
         <f>[1]CARTELLINO!LW$15</f>
@@ -45939,7 +45951,7 @@
       </c>
       <c r="MQ15" s="26" t="str">
         <f>[1]CARTELLINO!MT$15</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MR15" s="26" t="str">
         <f>[1]CARTELLINO!MU$15</f>
@@ -45971,7 +45983,7 @@
       </c>
       <c r="MY15" s="26" t="str">
         <f>[1]CARTELLINO!NB$15</f>
-        <v>P</v>
+        <v>p</v>
       </c>
       <c r="MZ15" s="26" t="str">
         <f>[1]CARTELLINO!NC$15</f>
@@ -46035,7 +46047,7 @@
       </c>
       <c r="NO15" s="26" t="str">
         <f>[1]CARTELLINO!NR$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NP15" s="26" t="str">
         <f>[1]CARTELLINO!NS$15</f>
@@ -46055,7 +46067,7 @@
       </c>
       <c r="NT15" s="26" t="str">
         <f>[1]CARTELLINO!NW$15</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NU15" s="26" t="str">
         <f>[1]CARTELLINO!NX$15</f>
@@ -47183,9 +47195,9 @@
         <f>[1]CARTELLINO!JJ$16</f>
         <v>0</v>
       </c>
-      <c r="JH16" s="46">
+      <c r="JH16" s="46" t="str">
         <f>[1]CARTELLINO!JK$16</f>
-        <v>0</v>
+        <v>k</v>
       </c>
       <c r="JI16" s="46">
         <f>[1]CARTELLINO!JL$16</f>
@@ -47423,9 +47435,9 @@
         <f>[1]CARTELLINO!LR$16</f>
         <v>0</v>
       </c>
-      <c r="LP16" s="46">
+      <c r="LP16" s="46" t="str">
         <f>[1]CARTELLINO!LS$16</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="LQ16" s="46">
         <f>[1]CARTELLINO!LT$16</f>
@@ -49203,7 +49215,7 @@
       </c>
       <c r="JL18" s="27" t="str">
         <f>[1]CARTELLINO!JO$18</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="JM18" s="27" t="str">
         <f>[1]CARTELLINO!JP$18</f>
@@ -49259,47 +49271,47 @@
       </c>
       <c r="JZ18" s="27" t="str">
         <f>[1]CARTELLINO!KC$18</f>
-        <v>M/R</v>
+        <v>m</v>
       </c>
       <c r="KA18" s="27" t="str">
         <f>[1]CARTELLINO!KD$18</f>
-        <v>N</v>
+        <v>m</v>
       </c>
       <c r="KB18" s="27" t="str">
         <f>[1]CARTELLINO!KE$18</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="KC18" s="27" t="str">
         <f>[1]CARTELLINO!KF$18</f>
-        <v>R</v>
+        <v>r</v>
       </c>
       <c r="KD18" s="27" t="str">
         <f>[1]CARTELLINO!KG$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KE18" s="27" t="str">
         <f>[1]CARTELLINO!KH$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KF18" s="27" t="str">
         <f>[1]CARTELLINO!KI$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KG18" s="27" t="str">
         <f>[1]CARTELLINO!KJ$18</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="KH18" s="27" t="str">
         <f>[1]CARTELLINO!KK$18</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="KI18" s="27" t="str">
         <f>[1]CARTELLINO!KL$18</f>
-        <v>-</v>
+        <v>r</v>
       </c>
       <c r="KJ18" s="27" t="str">
         <f>[1]CARTELLINO!KM$18</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="KK18" s="27" t="str">
         <f>[1]CARTELLINO!KN$18</f>
@@ -49399,19 +49411,19 @@
       </c>
       <c r="LI18" s="27" t="str">
         <f>[1]CARTELLINO!LL$18</f>
-        <v>m/R</v>
+        <v>-</v>
       </c>
       <c r="LJ18" s="27" t="str">
         <f>[1]CARTELLINO!LM$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LK18" s="27" t="str">
         <f>[1]CARTELLINO!LN$18</f>
-        <v>m</v>
+        <v>-</v>
       </c>
       <c r="LL18" s="27" t="str">
         <f>[1]CARTELLINO!LO$18</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="LM18" s="27" t="str">
         <f>[1]CARTELLINO!LP$18</f>
@@ -49431,7 +49443,7 @@
       </c>
       <c r="LQ18" s="27" t="str">
         <f>[1]CARTELLINO!LT$18</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="LR18" s="27" t="str">
         <f>[1]CARTELLINO!LU$18</f>
@@ -49439,23 +49451,23 @@
       </c>
       <c r="LS18" s="27" t="str">
         <f>[1]CARTELLINO!LV$18</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="LT18" s="27" t="str">
         <f>[1]CARTELLINO!LW$18</f>
-        <v>m/R</v>
+        <v>S</v>
       </c>
       <c r="LU18" s="27" t="str">
         <f>[1]CARTELLINO!LX$18</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="LV18" s="27" t="str">
         <f>[1]CARTELLINO!LY$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LW18" s="27" t="str">
         <f>[1]CARTELLINO!LZ$18</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="LX18" s="27" t="str">
         <f>[1]CARTELLINO!MA$18</f>
@@ -49467,7 +49479,7 @@
       </c>
       <c r="LZ18" s="27" t="str">
         <f>[1]CARTELLINO!MC$18</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="MA18" s="27" t="str">
         <f>[1]CARTELLINO!MD$18</f>
@@ -49563,11 +49575,11 @@
       </c>
       <c r="MX18" s="27" t="str">
         <f>[1]CARTELLINO!NA$18</f>
-        <v>P</v>
+        <v>M/R</v>
       </c>
       <c r="MY18" s="27" t="str">
         <f>[1]CARTELLINO!NB$18</f>
-        <v>M</v>
+        <v>P</v>
       </c>
       <c r="MZ18" s="27" t="str">
         <f>[1]CARTELLINO!NC$18</f>
@@ -49631,51 +49643,51 @@
       </c>
       <c r="NO18" s="27" t="str">
         <f>[1]CARTELLINO!NR$18</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="NP18" s="27" t="str">
         <f>[1]CARTELLINO!NS$18</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NQ18" s="27" t="str">
         <f>[1]CARTELLINO!NT$18</f>
-        <v>m</v>
+        <v>M</v>
       </c>
       <c r="NR18" s="27" t="str">
         <f>[1]CARTELLINO!NU$18</f>
-        <v>m</v>
+        <v>N</v>
       </c>
       <c r="NS18" s="27" t="str">
         <f>[1]CARTELLINO!NV$18</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="NT18" s="27" t="str">
         <f>[1]CARTELLINO!NW$18</f>
-        <v>m</v>
+        <v>R</v>
       </c>
       <c r="NU18" s="27" t="str">
         <f>[1]CARTELLINO!NX$18</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="NV18" s="27" t="str">
         <f>[1]CARTELLINO!NY$18</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="NW18" s="27" t="str">
         <f>[1]CARTELLINO!NZ$18</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="NX18" s="27" t="str">
         <f>[1]CARTELLINO!OA$18</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="NY18" s="27" t="str">
         <f>[1]CARTELLINO!OB$18</f>
-        <v>p</v>
+        <v>R</v>
       </c>
       <c r="NZ18" s="27" t="str">
         <f>[1]CARTELLINO!OC$18</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="OA18" s="27" t="str">
         <f>[1]CARTELLINO!OD$18</f>
@@ -50867,53 +50879,53 @@
         <f>[1]CARTELLINO!KF$19</f>
         <v>0</v>
       </c>
-      <c r="KD19" s="46" t="str">
+      <c r="KD19" s="46">
         <f>[1]CARTELLINO!KG$19</f>
-        <v>k</v>
-      </c>
-      <c r="KE19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KE19" s="46">
         <f>[1]CARTELLINO!KH$19</f>
-        <v>k</v>
-      </c>
-      <c r="KF19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KF19" s="46">
         <f>[1]CARTELLINO!KI$19</f>
-        <v>k</v>
-      </c>
-      <c r="KG19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KG19" s="46">
         <f>[1]CARTELLINO!KJ$19</f>
-        <v>k</v>
-      </c>
-      <c r="KH19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KH19" s="46">
         <f>[1]CARTELLINO!KK$19</f>
-        <v>k</v>
-      </c>
-      <c r="KI19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KI19" s="46">
         <f>[1]CARTELLINO!KL$19</f>
-        <v>k</v>
-      </c>
-      <c r="KJ19" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="KJ19" s="46">
         <f>[1]CARTELLINO!KM$19</f>
-        <v>k</v>
+        <v>0</v>
       </c>
       <c r="KK19" s="46" t="str">
         <f>[1]CARTELLINO!KN$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KL19" s="46" t="str">
         <f>[1]CARTELLINO!KO$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KM19" s="46" t="str">
         <f>[1]CARTELLINO!KP$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KN19" s="46" t="str">
         <f>[1]CARTELLINO!KQ$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KO19" s="46" t="str">
         <f>[1]CARTELLINO!KR$19</f>
-        <v>k</v>
+        <v>f</v>
       </c>
       <c r="KP19" s="46" t="str">
         <f>[1]CARTELLINO!KS$19</f>
@@ -50991,21 +51003,21 @@
         <f>[1]CARTELLINO!LK$19</f>
         <v>f</v>
       </c>
-      <c r="LI19" s="46">
+      <c r="LI19" s="46" t="str">
         <f>[1]CARTELLINO!LL$19</f>
-        <v>0</v>
-      </c>
-      <c r="LJ19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LJ19" s="46" t="str">
         <f>[1]CARTELLINO!LM$19</f>
-        <v>0</v>
-      </c>
-      <c r="LK19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LK19" s="46" t="str">
         <f>[1]CARTELLINO!LN$19</f>
-        <v>0</v>
-      </c>
-      <c r="LL19" s="46">
+        <v>k</v>
+      </c>
+      <c r="LL19" s="46" t="str">
         <f>[1]CARTELLINO!LO$19</f>
-        <v>0</v>
+        <v>k</v>
       </c>
       <c r="LM19" s="46">
         <f>[1]CARTELLINO!LP$19</f>
@@ -52855,23 +52867,23 @@
       </c>
       <c r="JZ21" s="28" t="str">
         <f>[1]CARTELLINO!KC$21</f>
-        <v>P</v>
+        <v>M/R</v>
       </c>
       <c r="KA21" s="28" t="str">
         <f>[1]CARTELLINO!KD$21</f>
-        <v>p</v>
+        <v>N</v>
       </c>
       <c r="KB21" s="28" t="str">
         <f>[1]CARTELLINO!KE$21</f>
-        <v>m</v>
+        <v>S</v>
       </c>
       <c r="KC21" s="28" t="str">
         <f>[1]CARTELLINO!KF$21</f>
-        <v>r</v>
+        <v>R</v>
       </c>
       <c r="KD21" s="28" t="str">
         <f>[1]CARTELLINO!KG$21</f>
-        <v>m/R</v>
+        <v>p</v>
       </c>
       <c r="KE21" s="28" t="str">
         <f>[1]CARTELLINO!KH$21</f>
@@ -52911,7 +52923,7 @@
       </c>
       <c r="KN21" s="28" t="str">
         <f>[1]CARTELLINO!KQ$21</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="KO21" s="28" t="str">
         <f>[1]CARTELLINO!KR$21</f>
@@ -52919,31 +52931,31 @@
       </c>
       <c r="KP21" s="28" t="str">
         <f>[1]CARTELLINO!KS$21</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="KQ21" s="28" t="str">
         <f>[1]CARTELLINO!KT$21</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KR21" s="28" t="str">
         <f>[1]CARTELLINO!KU$21</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="KS21" s="28" t="str">
         <f>[1]CARTELLINO!KV$21</f>
-        <v>m/R</v>
+        <v>S</v>
       </c>
       <c r="KT21" s="28" t="str">
         <f>[1]CARTELLINO!KW$21</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="KU21" s="28" t="str">
         <f>[1]CARTELLINO!KX$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="KV21" s="28" t="str">
         <f>[1]CARTELLINO!KY$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="KW21" s="28" t="str">
         <f>[1]CARTELLINO!KZ$21</f>
@@ -52959,7 +52971,7 @@
       </c>
       <c r="KZ21" s="28" t="str">
         <f>[1]CARTELLINO!LC$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LA21" s="28" t="str">
         <f>[1]CARTELLINO!LD$21</f>
@@ -53027,31 +53039,31 @@
       </c>
       <c r="LQ21" s="28" t="str">
         <f>[1]CARTELLINO!LT$21</f>
-        <v>r</v>
+        <v>P</v>
       </c>
       <c r="LR21" s="28" t="str">
         <f>[1]CARTELLINO!LU$21</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="LS21" s="28" t="str">
         <f>[1]CARTELLINO!LV$21</f>
-        <v>N</v>
+        <v>r</v>
       </c>
       <c r="LT21" s="28" t="str">
         <f>[1]CARTELLINO!LW$21</f>
-        <v>S</v>
+        <v>-</v>
       </c>
       <c r="LU21" s="28" t="str">
         <f>[1]CARTELLINO!LX$21</f>
-        <v>R</v>
+        <v>-</v>
       </c>
       <c r="LV21" s="28" t="str">
         <f>[1]CARTELLINO!LY$21</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LW21" s="28" t="str">
         <f>[1]CARTELLINO!LZ$21</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="LX21" s="28" t="str">
         <f>[1]CARTELLINO!MA$21</f>
@@ -53067,23 +53079,23 @@
       </c>
       <c r="MA21" s="28" t="str">
         <f>[1]CARTELLINO!MD$21</f>
-        <v>P</v>
+        <v>m</v>
       </c>
       <c r="MB21" s="28" t="str">
         <f>[1]CARTELLINO!ME$21</f>
-        <v>M/R</v>
+        <v>m/R</v>
       </c>
       <c r="MC21" s="28" t="str">
         <f>[1]CARTELLINO!MF$21</f>
-        <v>N</v>
+        <v>p</v>
       </c>
       <c r="MD21" s="28" t="str">
         <f>[1]CARTELLINO!MG$21</f>
-        <v>S</v>
+        <v>m</v>
       </c>
       <c r="ME21" s="28" t="str">
         <f>[1]CARTELLINO!MH$21</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="MF21" s="28" t="str">
         <f>[1]CARTELLINO!MI$21</f>
@@ -53159,7 +53171,7 @@
       </c>
       <c r="MX21" s="28" t="str">
         <f>[1]CARTELLINO!NA$21</f>
-        <v>M/R</v>
+        <v>m</v>
       </c>
       <c r="MY21" s="28" t="str">
         <f>[1]CARTELLINO!NB$21</f>
@@ -53187,11 +53199,11 @@
       </c>
       <c r="NE21" s="28" t="str">
         <f>[1]CARTELLINO!NH$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NF21" s="28" t="str">
         <f>[1]CARTELLINO!NI$21</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NG21" s="28" t="str">
         <f>[1]CARTELLINO!NJ$21</f>
@@ -53207,15 +53219,15 @@
       </c>
       <c r="NJ21" s="28" t="str">
         <f>[1]CARTELLINO!NM$21</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NK21" s="28" t="str">
         <f>[1]CARTELLINO!NN$21</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="NL21" s="28" t="str">
         <f>[1]CARTELLINO!NO$21</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="NM21" s="28" t="str">
         <f>[1]CARTELLINO!NP$21</f>
@@ -53243,7 +53255,7 @@
       </c>
       <c r="NS21" s="28" t="str">
         <f>[1]CARTELLINO!NV$21</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="NT21" s="28" t="str">
         <f>[1]CARTELLINO!NW$21</f>
@@ -54633,15 +54645,15 @@
       </c>
       <c r="LT22" s="46">
         <f>[1]CARTELLINO!LW$22</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="LU22" s="46">
         <f>[1]CARTELLINO!LX$22</f>
-        <v>0</v>
-      </c>
-      <c r="LV22" s="46">
+        <v>6</v>
+      </c>
+      <c r="LV22" s="46" t="str">
         <f>[1]CARTELLINO!LY$22</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="LW22" s="46">
         <f>[1]CARTELLINO!LZ$22</f>
@@ -54773,7 +54785,7 @@
       </c>
       <c r="NC22" s="46" t="str">
         <f>[1]CARTELLINO!NF$22</f>
-        <v>V</v>
+        <v>nl</v>
       </c>
       <c r="ND22" s="46" t="str">
         <f>[1]CARTELLINO!NG$22</f>
@@ -56399,7 +56411,7 @@
       </c>
       <c r="JM24" s="29" t="str">
         <f>[1]CARTELLINO!JP$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="JN24" s="29" t="str">
         <f>[1]CARTELLINO!JQ$24</f>
@@ -56451,11 +56463,11 @@
       </c>
       <c r="JZ24" s="29" t="str">
         <f>[1]CARTELLINO!KC$24</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="KA24" s="29" t="str">
         <f>[1]CARTELLINO!KD$24</f>
-        <v>r</v>
+        <v>M/R</v>
       </c>
       <c r="KB24" s="29" t="str">
         <f>[1]CARTELLINO!KE$24</f>
@@ -56515,7 +56527,7 @@
       </c>
       <c r="KP24" s="29" t="str">
         <f>[1]CARTELLINO!KS$24</f>
-        <v>M/R</v>
+        <v>P</v>
       </c>
       <c r="KQ24" s="29" t="str">
         <f>[1]CARTELLINO!KT$24</f>
@@ -56531,11 +56543,11 @@
       </c>
       <c r="KT24" s="29" t="str">
         <f>[1]CARTELLINO!KW$24</f>
-        <v>-</v>
+        <v>P</v>
       </c>
       <c r="KU24" s="29" t="str">
         <f>[1]CARTELLINO!KX$24</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KV24" s="29" t="str">
         <f>[1]CARTELLINO!KY$24</f>
@@ -56611,39 +56623,39 @@
       </c>
       <c r="LN24" s="29" t="str">
         <f>[1]CARTELLINO!LQ$24</f>
-        <v>p</v>
+        <v>-</v>
       </c>
       <c r="LO24" s="29" t="str">
         <f>[1]CARTELLINO!LR$24</f>
-        <v>P</v>
+        <v>-</v>
       </c>
       <c r="LP24" s="29" t="str">
         <f>[1]CARTELLINO!LS$24</f>
-        <v>m</v>
+        <v>M/R</v>
       </c>
       <c r="LQ24" s="29" t="str">
         <f>[1]CARTELLINO!LT$24</f>
-        <v>r</v>
+        <v>N</v>
       </c>
       <c r="LR24" s="29" t="str">
         <f>[1]CARTELLINO!LU$24</f>
-        <v>p</v>
+        <v>S</v>
       </c>
       <c r="LS24" s="29" t="str">
         <f>[1]CARTELLINO!LV$24</f>
-        <v>P</v>
+        <v>R</v>
       </c>
       <c r="LT24" s="29" t="str">
         <f>[1]CARTELLINO!LW$24</f>
-        <v>M</v>
+        <v>p</v>
       </c>
       <c r="LU24" s="29" t="str">
         <f>[1]CARTELLINO!LX$24</f>
-        <v>r</v>
+        <v>m</v>
       </c>
       <c r="LV24" s="29" t="str">
         <f>[1]CARTELLINO!LY$24</f>
-        <v>p</v>
+        <v>P</v>
       </c>
       <c r="LW24" s="29" t="str">
         <f>[1]CARTELLINO!LZ$24</f>
@@ -56651,7 +56663,7 @@
       </c>
       <c r="LX24" s="29" t="str">
         <f>[1]CARTELLINO!MA$24</f>
-        <v>M/R</v>
+        <v>r</v>
       </c>
       <c r="LY24" s="29" t="str">
         <f>[1]CARTELLINO!MB$24</f>
@@ -56751,19 +56763,19 @@
       </c>
       <c r="MW24" s="29" t="str">
         <f>[1]CARTELLINO!MZ$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MX24" s="29" t="str">
         <f>[1]CARTELLINO!NA$24</f>
-        <v>-</v>
+        <v>p</v>
       </c>
       <c r="MY24" s="29" t="str">
         <f>[1]CARTELLINO!NB$24</f>
-        <v>-</v>
+        <v>m</v>
       </c>
       <c r="MZ24" s="29" t="str">
         <f>[1]CARTELLINO!NC$24</f>
-        <v>R</v>
+        <v>m</v>
       </c>
       <c r="NA24" s="29" t="str">
         <f>[1]CARTELLINO!ND$24</f>
@@ -56771,7 +56783,7 @@
       </c>
       <c r="NB24" s="29" t="str">
         <f>[1]CARTELLINO!NE$24</f>
-        <v>M/R</v>
+        <v>-</v>
       </c>
       <c r="NC24" s="29" t="str">
         <f>[1]CARTELLINO!NF$24</f>
@@ -56827,7 +56839,7 @@
       </c>
       <c r="NP24" s="29" t="str">
         <f>[1]CARTELLINO!NS$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NQ24" s="29" t="str">
         <f>[1]CARTELLINO!NT$24</f>
@@ -56835,27 +56847,27 @@
       </c>
       <c r="NR24" s="29" t="str">
         <f>[1]CARTELLINO!NU$24</f>
-        <v>p</v>
+        <v>m/R</v>
       </c>
       <c r="NS24" s="29" t="str">
         <f>[1]CARTELLINO!NV$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NT24" s="29" t="str">
         <f>[1]CARTELLINO!NW$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NU24" s="29" t="str">
         <f>[1]CARTELLINO!NX$24</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="NV24" s="29" t="str">
         <f>[1]CARTELLINO!NY$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="NW24" s="29" t="str">
         <f>[1]CARTELLINO!NZ$24</f>
-        <v>m</v>
+        <v>r</v>
       </c>
       <c r="NX24" s="29" t="str">
         <f>[1]CARTELLINO!OA$24</f>
@@ -56867,7 +56879,7 @@
       </c>
       <c r="NZ24" s="29" t="str">
         <f>[1]CARTELLINO!OC$24</f>
-        <v>p</v>
+        <v>m</v>
       </c>
       <c r="OA24" s="29" t="str">
         <f>[1]CARTELLINO!OD$24</f>
@@ -58123,9 +58135,9 @@
         <f>[1]CARTELLINO!KV$25</f>
         <v>0</v>
       </c>
-      <c r="KT25" s="46" t="str">
+      <c r="KT25" s="46">
         <f>[1]CARTELLINO!KW$25</f>
-        <v>p</v>
+        <v>0</v>
       </c>
       <c r="KU25" s="46">
         <f>[1]CARTELLINO!KX$25</f>
@@ -58203,13 +58215,13 @@
         <f>[1]CARTELLINO!LP$25</f>
         <v>0</v>
       </c>
-      <c r="LN25" s="46">
+      <c r="LN25" s="46" t="str">
         <f>[1]CARTELLINO!LQ$25</f>
-        <v>0</v>
-      </c>
-      <c r="LO25" s="46">
+        <v>p</v>
+      </c>
+      <c r="LO25" s="46" t="str">
         <f>[1]CARTELLINO!LR$25</f>
-        <v>0</v>
+        <v>p</v>
       </c>
       <c r="LP25" s="46">
         <f>[1]CARTELLINO!LS$25</f>
@@ -58341,19 +58353,19 @@
       </c>
       <c r="MV25" s="46" t="str">
         <f>[1]CARTELLINO!MY$25</f>
-        <v>nl</v>
-      </c>
-      <c r="MW25" s="46" t="str">
+        <v>p</v>
+      </c>
+      <c r="MW25" s="46">
         <f>[1]CARTELLINO!MZ$25</f>
-        <v>nl</v>
-      </c>
-      <c r="MX25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="MX25" s="46">
         <f>[1]CARTELLINO!NA$25</f>
-        <v>pn</v>
-      </c>
-      <c r="MY25" s="46" t="str">
+        <v>0</v>
+      </c>
+      <c r="MY25" s="46">
         <f>[1]CARTELLINO!NB$25</f>
-        <v>x</v>
+        <v>0</v>
       </c>
       <c r="MZ25" s="46">
         <f>[1]CARTELLINO!NC$25</f>
@@ -58363,9 +58375,9 @@
         <f>[1]CARTELLINO!ND$25</f>
         <v>0</v>
       </c>
-      <c r="NB25" s="46">
+      <c r="NB25" s="46" t="str">
         <f>[1]CARTELLINO!NE$25</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="NC25" s="46" t="str">
         <f>[1]CARTELLINO!NF$25</f>
@@ -60063,7 +60075,7 @@
       </c>
       <c r="KD27" s="30" t="str">
         <f>[1]CARTELLINO!KG$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KE27" s="30" t="str">
         <f>[1]CARTELLINO!KH$27</f>
@@ -60083,7 +60095,7 @@
       </c>
       <c r="KI27" s="30" t="str">
         <f>[1]CARTELLINO!KL$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="KJ27" s="30" t="str">
         <f>[1]CARTELLINO!KM$27</f>
@@ -60103,7 +60115,7 @@
       </c>
       <c r="KN27" s="30" t="str">
         <f>[1]CARTELLINO!KQ$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="KO27" s="30" t="str">
         <f>[1]CARTELLINO!KR$27</f>
@@ -60163,7 +60175,7 @@
       </c>
       <c r="LC27" s="30" t="str">
         <f>[1]CARTELLINO!LF$27</f>
-        <v>M/R</v>
+        <v>M</v>
       </c>
       <c r="LD27" s="30" t="str">
         <f>[1]CARTELLINO!LG$27</f>
@@ -60187,7 +60199,7 @@
       </c>
       <c r="LI27" s="30" t="str">
         <f>[1]CARTELLINO!LL$27</f>
-        <v>M</v>
+        <v>M/R</v>
       </c>
       <c r="LJ27" s="30" t="str">
         <f>[1]CARTELLINO!LM$27</f>
@@ -60203,7 +60215,7 @@
       </c>
       <c r="LM27" s="30" t="str">
         <f>[1]CARTELLINO!LP$27</f>
-        <v>r</v>
+        <v>-</v>
       </c>
       <c r="LN27" s="30" t="str">
         <f>[1]CARTELLINO!LQ$27</f>
@@ -60211,7 +60223,7 @@
       </c>
       <c r="LO27" s="30" t="str">
         <f>[1]CARTELLINO!LR$27</f>
-        <v>m/R</v>
+        <v>m</v>
       </c>
       <c r="LP27" s="30" t="str">
         <f>[1]CARTELLINO!LS$27</f>
@@ -60219,11 +60231,11 @@
       </c>
       <c r="LQ27" s="30" t="str">
         <f>[1]CARTELLINO!LT$27</f>
-        <v>m</v>
+        <v>p</v>
       </c>
       <c r="LR27" s="30" t="str">
         <f>[1]CARTELLINO!LU$27</f>
-        <v>r</v>
+        <v>m/R</v>
       </c>
       <c r="LS27" s="30" t="str">
         <f>[1]CARTELLINO!LV$27</f>
@@ -60247,19 +60259,19 @@
       </c>
       <c r="LX27" s="30" t="str">
         <f>[1]CARTELLINO!MA$27</f>
-        <v>m</v>
+        <v>m/R</v>
       </c>
       <c r="LY27" s="30" t="str">
         <f>[1]CARTELLINO!MB$27</f>
-        <v>r</v>
+        <v>p</v>
       </c>
       <c r="LZ27" s="30" t="str">
         <f>[1]CARTELLINO!MC$27</f>
-        <v>p</v>
+        <v>r</v>
       </c>
       <c r="MA27" s="30" t="str">
         <f>[1]CARTELLINO!MD$27</f>
-        <v>m</v>
+        <v>P</v>
       </c>
       <c r="MB27" s="30" t="str">
         <f>[1]CARTELLINO!ME$27</f>
@@ -61795,9 +61807,9 @@
         <f>[1]CARTELLINO!LO$28</f>
         <v>0</v>
       </c>
-      <c r="LM28" s="62">
+      <c r="LM28" s="62" t="str">
         <f>[1]CARTELLINO!LP$28</f>
-        <v>0</v>
+        <v>r</v>
       </c>
       <c r="LN28" s="62">
         <f>[1]CARTELLINO!LQ$28</f>
@@ -62956,10 +62968,10 @@
         <v>FABBRI</v>
       </c>
       <c r="KA29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KB29" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KC29" s="63" t="str">
         <v>SARTI</v>
@@ -62968,7 +62980,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KE29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KF29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -62983,7 +62995,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KJ29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KK29" s="63" t="str">
         <v>BERARDI</v>
@@ -62998,28 +63010,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="KO29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KP29" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KQ29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KR29" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KS29" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KT29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KU29" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KW29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63031,7 +63043,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KZ29" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LA29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63043,10 +63055,10 @@
         <v>BARBIERI</v>
       </c>
       <c r="LD29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LE29" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LF29" s="63" t="str">
         <v>BIANCHI</v>
@@ -63061,7 +63073,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LJ29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LK29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63073,28 +63085,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="LN29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LO29" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="LP29" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LQ29" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LR29" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LS29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LT29" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="LU29" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LV29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63103,10 +63115,10 @@
         <v>SARTI</v>
       </c>
       <c r="LX29" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LY29" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LZ29" s="63" t="str">
         <v>VOLPINI</v>
@@ -63168,8 +63180,8 @@
       <c r="MS29" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT29" s="63">
-        <v>0</v>
+      <c r="MT29" s="63" t="str">
+        <v>VOLPINI</v>
       </c>
       <c r="MU29" s="63" t="str">
         <v>GHIOTTI</v>
@@ -63183,8 +63195,8 @@
       <c r="MX29" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY29" s="63">
-        <v>0</v>
+      <c r="MY29" s="63" t="str">
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ29" s="63" t="str">
         <v>BARBIERI</v>
@@ -64047,7 +64059,7 @@
         <v>BERARDI</v>
       </c>
       <c r="JX30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="JY30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64056,10 +64068,10 @@
         <v>FABBRI</v>
       </c>
       <c r="KA30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KB30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KC30" s="63" t="str">
         <v>SARTI</v>
@@ -64068,7 +64080,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KE30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KF30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64083,7 +64095,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KJ30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KK30" s="63" t="str">
         <v>BERARDI</v>
@@ -64098,28 +64110,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="KO30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KP30" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KQ30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KR30" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KS30" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KT30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KU30" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KV30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KW30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64131,7 +64143,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KZ30" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LA30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64143,10 +64155,10 @@
         <v>BARBIERI</v>
       </c>
       <c r="LD30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LE30" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LF30" s="63" t="str">
         <v>BIANCHI</v>
@@ -64161,7 +64173,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LJ30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LK30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64179,34 +64191,34 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LP30" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LQ30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LR30" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LS30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LT30" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="LU30" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LV30" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LW30" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LX30" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LY30" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LZ30" s="63" t="str">
         <v>VOLPINI</v>
@@ -64268,8 +64280,8 @@
       <c r="MS30" s="63" t="str">
         <v>BIANCHI</v>
       </c>
-      <c r="MT30" s="63">
-        <v>0</v>
+      <c r="MT30" s="63" t="str">
+        <v>VOLPINI</v>
       </c>
       <c r="MU30" s="63" t="str">
         <v>GHIOTTI</v>
@@ -64283,8 +64295,8 @@
       <c r="MX30" s="63" t="str">
         <v>VOLPINI</v>
       </c>
-      <c r="MY30" s="63">
-        <v>0</v>
+      <c r="MY30" s="63" t="str">
+        <v>MICHELOT.</v>
       </c>
       <c r="MZ30" s="63" t="str">
         <v>BARBIERI</v>
@@ -65153,10 +65165,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JZ31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KA31" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KB31" s="63" t="str">
         <v>SARTI</v>
@@ -65165,7 +65177,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KD31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KE31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65180,7 +65192,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KI31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KJ31" s="63" t="str">
         <v>BERARDI</v>
@@ -65195,28 +65207,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="KN31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KO31" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KP31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KQ31" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KR31" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KS31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BARBIERI</v>
       </c>
       <c r="KT31" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KV31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65228,7 +65240,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KY31" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KZ31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65240,10 +65252,10 @@
         <v>BARBIERI</v>
       </c>
       <c r="LC31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LD31" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LE31" s="63" t="str">
         <v>BIANCHI</v>
@@ -65258,7 +65270,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LI31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LJ31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65276,22 +65288,22 @@
         <v>MICHELOT.</v>
       </c>
       <c r="LO31" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LP31" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LQ31" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LR31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LS31" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="LT31" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LU31" s="63" t="str">
         <v>GHIOTTI</v>
@@ -65300,10 +65312,10 @@
         <v>SARTI</v>
       </c>
       <c r="LW31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LX31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LY31" s="63" t="str">
         <v>VOLPINI</v>
@@ -65381,7 +65393,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MX31" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MY31" s="63" t="str">
         <v>BARBIERI</v>
@@ -65393,7 +65405,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="NB31" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BARBIERI</v>
       </c>
     </row>
     <row r="32" spans="1:404" x14ac:dyDescent="0.25">
@@ -66190,7 +66202,7 @@
         <v>BIANCHI</v>
       </c>
       <c r="JE32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="JF32" s="63" t="str">
         <v>FABBRI</v>
@@ -66253,10 +66265,10 @@
         <v>FABBRI</v>
       </c>
       <c r="JZ32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BERARDI</v>
       </c>
       <c r="KA32" s="63" t="str">
-        <v>BARBIERI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KB32" s="63" t="str">
         <v>SARTI</v>
@@ -66265,7 +66277,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="KD32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KE32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66280,7 +66292,7 @@
         <v>BARBIERI</v>
       </c>
       <c r="KI32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KJ32" s="63" t="str">
         <v>BERARDI</v>
@@ -66295,28 +66307,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="KN32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>FABBRI</v>
       </c>
       <c r="KO32" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KP32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BERARDI</v>
       </c>
       <c r="KQ32" s="63" t="str">
-        <v>SARTI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KR32" s="63" t="str">
         <v>BARBIERI</v>
       </c>
       <c r="KS32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>GHIOTTI</v>
       </c>
       <c r="KT32" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="KU32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="KV32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66328,7 +66340,7 @@
         <v>FABBRI</v>
       </c>
       <c r="KY32" s="63" t="str">
-        <v>PAZZAGLIA</v>
+        <v>VOLPINI</v>
       </c>
       <c r="KZ32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66340,10 +66352,10 @@
         <v>BARBIERI</v>
       </c>
       <c r="LC32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>SARTI</v>
       </c>
       <c r="LD32" s="63" t="str">
-        <v>VOLPINI</v>
+        <v>PAZZAGLIA</v>
       </c>
       <c r="LE32" s="63" t="str">
         <v>BIANCHI</v>
@@ -66358,7 +66370,7 @@
         <v>BERARDI</v>
       </c>
       <c r="LI32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>FABBRI</v>
       </c>
       <c r="LJ32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66370,28 +66382,28 @@
         <v>BARBIERI</v>
       </c>
       <c r="LM32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LN32" s="63" t="str">
         <v>MICHELOT.</v>
       </c>
       <c r="LO32" s="63" t="str">
-        <v>FABBRI</v>
+        <v>VOLPINI</v>
       </c>
       <c r="LP32" s="63" t="str">
-        <v>GHIOTTI</v>
+        <v>BIANCHI</v>
       </c>
       <c r="LQ32" s="63" t="str">
         <v>SARTI</v>
       </c>
       <c r="LR32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LS32" s="63" t="str">
         <v>PAZZAGLIA</v>
       </c>
       <c r="LT32" s="63" t="str">
-        <v>MICHELOT.</v>
+        <v>BARBIERI</v>
       </c>
       <c r="LU32" s="63" t="str">
         <v>GHIOTTI</v>
@@ -66400,10 +66412,10 @@
         <v>SARTI</v>
       </c>
       <c r="LW32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="LX32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>FABBRI</v>
       </c>
       <c r="LY32" s="63" t="str">
         <v>VOLPINI</v>
@@ -66481,7 +66493,7 @@
         <v>VOLPINI</v>
       </c>
       <c r="MX32" s="63" t="str">
-        <v>BERARDI</v>
+        <v>MICHELOT.</v>
       </c>
       <c r="MY32" s="63" t="str">
         <v>BARBIERI</v>
@@ -66493,7 +66505,7 @@
         <v>PAZZAGLIA</v>
       </c>
       <c r="NB32" s="63" t="str">
-        <v>BIANCHI</v>
+        <v>BARBIERI</v>
       </c>
     </row>
     <row r="33" spans="1:285" x14ac:dyDescent="0.25">
